--- a/AutosurveillanceTemplates/Q_GRAV.xlsx
+++ b/AutosurveillanceTemplates/Q_GRAV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndhuy\AppData\Roaming\Microsoft\AddIns\AutosurveillanceTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E36021-FA0A-4E09-A707-913226DAE216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6715B49A-2137-4B64-A041-D56FD6D96278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28905" yWindow="3255" windowWidth="14610" windowHeight="15585" tabRatio="777" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="3135" windowWidth="29040" windowHeight="15720" tabRatio="777" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REX controleurs" sheetId="23" state="hidden" r:id="rId1"/>
@@ -5913,7 +5913,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="807">
+  <cellXfs count="808">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8600,7 +8600,10 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="169" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="172" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="52" fillId="0" borderId="171" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="52" fillId="0" borderId="172" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="33" borderId="178" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -41753,11 +41756,11 @@
       <c r="J3" s="763"/>
       <c r="K3" s="763"/>
       <c r="L3" s="763"/>
-      <c r="M3" s="781" t="s">
+      <c r="M3" s="782" t="s">
         <v>353</v>
       </c>
-      <c r="N3" s="781"/>
-      <c r="O3" s="781"/>
+      <c r="N3" s="782"/>
+      <c r="O3" s="782"/>
       <c r="P3" s="763"/>
       <c r="Q3" s="763"/>
       <c r="R3" s="765"/>
@@ -41785,11 +41788,11 @@
       <c r="J4" s="763"/>
       <c r="K4" s="763"/>
       <c r="L4" s="763"/>
-      <c r="M4" s="781" t="s">
+      <c r="M4" s="782" t="s">
         <v>392</v>
       </c>
-      <c r="N4" s="781"/>
-      <c r="O4" s="781"/>
+      <c r="N4" s="782"/>
+      <c r="O4" s="782"/>
       <c r="P4" s="763"/>
       <c r="Q4" s="763"/>
       <c r="R4" s="765"/>
@@ -41817,11 +41820,11 @@
       <c r="J5" s="763"/>
       <c r="K5" s="763"/>
       <c r="L5" s="763"/>
-      <c r="M5" s="781" t="s">
+      <c r="M5" s="782" t="s">
         <v>393</v>
       </c>
-      <c r="N5" s="781"/>
-      <c r="O5" s="781"/>
+      <c r="N5" s="782"/>
+      <c r="O5" s="782"/>
       <c r="P5" s="763"/>
       <c r="Q5" s="763"/>
       <c r="R5" s="765"/>
@@ -41849,14 +41852,14 @@
       <c r="J6" s="764"/>
       <c r="K6" s="764"/>
       <c r="L6" s="764"/>
-      <c r="M6" s="782" t="s">
+      <c r="M6" s="783" t="s">
         <v>394</v>
       </c>
-      <c r="N6" s="782"/>
-      <c r="O6" s="782"/>
-      <c r="P6" s="764"/>
-      <c r="Q6" s="764"/>
-      <c r="R6" s="766"/>
+      <c r="N6" s="783"/>
+      <c r="O6" s="783"/>
+      <c r="P6" s="766"/>
+      <c r="Q6" s="766"/>
+      <c r="R6" s="767"/>
       <c r="S6" s="384"/>
       <c r="T6" s="417"/>
       <c r="U6" s="417"/>
@@ -41893,24 +41896,24 @@
     </row>
     <row r="8" spans="2:25" s="367" customFormat="1" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="374"/>
-      <c r="C8" s="767" t="s">
+      <c r="C8" s="768" t="s">
         <v>365</v>
       </c>
-      <c r="D8" s="768"/>
-      <c r="E8" s="768"/>
-      <c r="F8" s="768"/>
-      <c r="G8" s="768"/>
-      <c r="H8" s="768"/>
-      <c r="I8" s="768"/>
-      <c r="J8" s="768"/>
-      <c r="K8" s="768"/>
-      <c r="L8" s="768"/>
-      <c r="M8" s="768"/>
-      <c r="N8" s="768"/>
-      <c r="O8" s="768"/>
-      <c r="P8" s="768"/>
-      <c r="Q8" s="768"/>
-      <c r="R8" s="769"/>
+      <c r="D8" s="769"/>
+      <c r="E8" s="769"/>
+      <c r="F8" s="769"/>
+      <c r="G8" s="769"/>
+      <c r="H8" s="769"/>
+      <c r="I8" s="769"/>
+      <c r="J8" s="769"/>
+      <c r="K8" s="769"/>
+      <c r="L8" s="769"/>
+      <c r="M8" s="769"/>
+      <c r="N8" s="769"/>
+      <c r="O8" s="769"/>
+      <c r="P8" s="769"/>
+      <c r="Q8" s="769"/>
+      <c r="R8" s="770"/>
       <c r="S8" s="375"/>
       <c r="T8" s="418"/>
       <c r="U8" s="418"/>
@@ -41948,22 +41951,22 @@
     <row r="10" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B10" s="376"/>
       <c r="C10" s="429"/>
-      <c r="D10" s="772" t="s">
+      <c r="D10" s="773" t="s">
         <v>397</v>
       </c>
-      <c r="E10" s="773"/>
-      <c r="F10" s="773"/>
-      <c r="G10" s="773"/>
-      <c r="H10" s="773"/>
-      <c r="I10" s="773"/>
-      <c r="J10" s="773"/>
-      <c r="K10" s="773"/>
-      <c r="L10" s="773"/>
-      <c r="M10" s="773"/>
-      <c r="N10" s="773"/>
-      <c r="O10" s="773"/>
-      <c r="P10" s="773"/>
-      <c r="Q10" s="774"/>
+      <c r="E10" s="774"/>
+      <c r="F10" s="774"/>
+      <c r="G10" s="774"/>
+      <c r="H10" s="774"/>
+      <c r="I10" s="774"/>
+      <c r="J10" s="774"/>
+      <c r="K10" s="774"/>
+      <c r="L10" s="774"/>
+      <c r="M10" s="774"/>
+      <c r="N10" s="774"/>
+      <c r="O10" s="774"/>
+      <c r="P10" s="774"/>
+      <c r="Q10" s="775"/>
       <c r="R10" s="430"/>
       <c r="S10" s="377"/>
     </row>
@@ -41975,10 +41978,10 @@
       </c>
       <c r="E11" s="749"/>
       <c r="F11" s="750"/>
-      <c r="G11" s="775"/>
-      <c r="H11" s="776"/>
-      <c r="I11" s="776"/>
-      <c r="J11" s="777"/>
+      <c r="G11" s="776"/>
+      <c r="H11" s="777"/>
+      <c r="I11" s="777"/>
+      <c r="J11" s="778"/>
       <c r="K11" s="748" t="s">
         <v>359</v>
       </c>
@@ -42600,22 +42603,22 @@
     <row r="32" spans="2:22" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B32" s="376"/>
       <c r="C32" s="431"/>
-      <c r="D32" s="772" t="s">
+      <c r="D32" s="773" t="s">
         <v>195</v>
       </c>
-      <c r="E32" s="773"/>
-      <c r="F32" s="773"/>
-      <c r="G32" s="773"/>
-      <c r="H32" s="773"/>
-      <c r="I32" s="773"/>
-      <c r="J32" s="773"/>
-      <c r="K32" s="773"/>
-      <c r="L32" s="773"/>
-      <c r="M32" s="773"/>
-      <c r="N32" s="783" t="s">
+      <c r="E32" s="774"/>
+      <c r="F32" s="774"/>
+      <c r="G32" s="774"/>
+      <c r="H32" s="774"/>
+      <c r="I32" s="774"/>
+      <c r="J32" s="774"/>
+      <c r="K32" s="774"/>
+      <c r="L32" s="774"/>
+      <c r="M32" s="774"/>
+      <c r="N32" s="784" t="s">
         <v>396</v>
       </c>
-      <c r="O32" s="783"/>
+      <c r="O32" s="784"/>
       <c r="P32" s="446"/>
       <c r="Q32" s="403"/>
       <c r="R32" s="432"/>
@@ -42624,29 +42627,29 @@
     <row r="33" spans="2:25" s="388" customFormat="1" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B33" s="386"/>
       <c r="C33" s="434"/>
-      <c r="D33" s="778" t="s">
+      <c r="D33" s="779" t="s">
         <v>370</v>
       </c>
-      <c r="E33" s="779"/>
-      <c r="F33" s="780"/>
-      <c r="G33" s="778" t="s">
+      <c r="E33" s="780"/>
+      <c r="F33" s="781"/>
+      <c r="G33" s="779" t="s">
         <v>366</v>
       </c>
-      <c r="H33" s="780"/>
-      <c r="I33" s="778" t="s">
+      <c r="H33" s="781"/>
+      <c r="I33" s="779" t="s">
         <v>395</v>
       </c>
-      <c r="J33" s="780"/>
-      <c r="K33" s="784" t="s">
+      <c r="J33" s="781"/>
+      <c r="K33" s="785" t="s">
         <v>385</v>
       </c>
-      <c r="L33" s="785"/>
-      <c r="M33" s="786"/>
-      <c r="N33" s="784" t="s">
+      <c r="L33" s="786"/>
+      <c r="M33" s="787"/>
+      <c r="N33" s="785" t="s">
         <v>386</v>
       </c>
-      <c r="O33" s="785"/>
-      <c r="P33" s="786"/>
+      <c r="O33" s="786"/>
+      <c r="P33" s="787"/>
       <c r="Q33" s="404"/>
       <c r="R33" s="435"/>
       <c r="S33" s="387"/>
@@ -42675,10 +42678,10 @@
       <c r="H34" s="423" t="s">
         <v>406</v>
       </c>
-      <c r="I34" s="770" t="s">
+      <c r="I34" s="771" t="s">
         <v>387</v>
       </c>
-      <c r="J34" s="771"/>
+      <c r="J34" s="772"/>
       <c r="K34" s="394" t="s">
         <v>373</v>
       </c>
@@ -42718,14 +42721,14 @@
       </c>
       <c r="G35" s="398"/>
       <c r="H35" s="407"/>
-      <c r="I35" s="787"/>
-      <c r="J35" s="788"/>
+      <c r="I35" s="788"/>
+      <c r="J35" s="789"/>
       <c r="K35" s="401" t="str">
         <f>IF(AND(E35&lt;&gt;"",G35&lt;&gt;""),(E35+G35)/2,IF(AND(I35&lt;&gt;"",G35&lt;&gt;""),(I35+G35)/2,""))</f>
         <v/>
       </c>
       <c r="L35" s="402" t="str">
-        <f>IF(AND(E35&lt;&gt;"",G35&lt;&gt;""),(E35-G35),IF(AND(I35&lt;&gt;"",G35&lt;&gt;""),(I35-G35),""))</f>
+        <f>IF(AND(I35&lt;&gt;"",G35&lt;&gt;""),(I35-G35),IF(AND(E35&lt;&gt;"",G35&lt;&gt;""),(E35-G35),""))</f>
         <v/>
       </c>
       <c r="M35" s="444" t="str">
@@ -42737,7 +42740,7 @@
         <v/>
       </c>
       <c r="O35" s="402" t="str">
-        <f>IF(AND(E35&lt;&gt;"",H35&lt;&gt;""),(E35-I35),IF(AND(H35&lt;&gt;"",I35&lt;&gt;""),(H35-I35),""))</f>
+        <f>IF(AND(H35&lt;&gt;"",I35&lt;&gt;""),(H35-I35),IF(AND(E35&lt;&gt;"",I35&lt;&gt;""),(E35-I35),""))</f>
         <v/>
       </c>
       <c r="P35" s="444" t="str">
@@ -42802,24 +42805,24 @@
     </row>
     <row r="38" spans="2:25" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B38" s="376"/>
-      <c r="C38" s="767" t="s">
+      <c r="C38" s="768" t="s">
         <v>375</v>
       </c>
-      <c r="D38" s="768"/>
-      <c r="E38" s="768"/>
-      <c r="F38" s="768"/>
-      <c r="G38" s="768"/>
-      <c r="H38" s="768"/>
-      <c r="I38" s="768"/>
-      <c r="J38" s="768"/>
-      <c r="K38" s="768"/>
-      <c r="L38" s="768"/>
-      <c r="M38" s="768"/>
-      <c r="N38" s="768"/>
-      <c r="O38" s="768"/>
-      <c r="P38" s="768"/>
-      <c r="Q38" s="768"/>
-      <c r="R38" s="769"/>
+      <c r="D38" s="769"/>
+      <c r="E38" s="769"/>
+      <c r="F38" s="769"/>
+      <c r="G38" s="769"/>
+      <c r="H38" s="769"/>
+      <c r="I38" s="769"/>
+      <c r="J38" s="769"/>
+      <c r="K38" s="769"/>
+      <c r="L38" s="769"/>
+      <c r="M38" s="769"/>
+      <c r="N38" s="769"/>
+      <c r="O38" s="769"/>
+      <c r="P38" s="769"/>
+      <c r="Q38" s="769"/>
+      <c r="R38" s="770"/>
       <c r="S38" s="377"/>
     </row>
     <row r="39" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -42845,22 +42848,22 @@
     <row r="40" spans="2:25" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B40" s="376"/>
       <c r="C40" s="431"/>
-      <c r="D40" s="796" t="s">
+      <c r="D40" s="797" t="s">
         <v>119</v>
       </c>
-      <c r="E40" s="796"/>
-      <c r="F40" s="796"/>
-      <c r="G40" s="796"/>
-      <c r="H40" s="796"/>
-      <c r="I40" s="796"/>
-      <c r="J40" s="796"/>
-      <c r="K40" s="796"/>
-      <c r="L40" s="796"/>
-      <c r="M40" s="796"/>
-      <c r="N40" s="796"/>
-      <c r="O40" s="796"/>
-      <c r="P40" s="796"/>
-      <c r="Q40" s="796"/>
+      <c r="E40" s="797"/>
+      <c r="F40" s="797"/>
+      <c r="G40" s="797"/>
+      <c r="H40" s="797"/>
+      <c r="I40" s="797"/>
+      <c r="J40" s="797"/>
+      <c r="K40" s="797"/>
+      <c r="L40" s="797"/>
+      <c r="M40" s="797"/>
+      <c r="N40" s="797"/>
+      <c r="O40" s="797"/>
+      <c r="P40" s="797"/>
+      <c r="Q40" s="797"/>
       <c r="R40" s="432"/>
       <c r="S40" s="377"/>
       <c r="U40" s="408" t="s">
@@ -42870,24 +42873,24 @@
     <row r="41" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B41" s="376"/>
       <c r="C41" s="431"/>
-      <c r="D41" s="797" t="s">
+      <c r="D41" s="798" t="s">
         <v>46</v>
       </c>
-      <c r="E41" s="797"/>
-      <c r="F41" s="797"/>
-      <c r="G41" s="797"/>
-      <c r="H41" s="797"/>
-      <c r="I41" s="797"/>
-      <c r="J41" s="797" t="s">
+      <c r="E41" s="798"/>
+      <c r="F41" s="798"/>
+      <c r="G41" s="798"/>
+      <c r="H41" s="798"/>
+      <c r="I41" s="798"/>
+      <c r="J41" s="798" t="s">
         <v>322</v>
       </c>
-      <c r="K41" s="797"/>
-      <c r="L41" s="797"/>
-      <c r="M41" s="797"/>
-      <c r="N41" s="797" t="s">
+      <c r="K41" s="798"/>
+      <c r="L41" s="798"/>
+      <c r="M41" s="798"/>
+      <c r="N41" s="798" t="s">
         <v>189</v>
       </c>
-      <c r="O41" s="797"/>
+      <c r="O41" s="798"/>
       <c r="P41" s="426" t="s">
         <v>341</v>
       </c>
@@ -43307,52 +43310,52 @@
     <row r="52" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B52" s="376"/>
       <c r="C52" s="431"/>
-      <c r="D52" s="798" t="s">
+      <c r="D52" s="799" t="s">
         <v>62</v>
       </c>
-      <c r="E52" s="799"/>
-      <c r="F52" s="799"/>
-      <c r="G52" s="799"/>
-      <c r="H52" s="799"/>
-      <c r="I52" s="799"/>
-      <c r="J52" s="799"/>
-      <c r="K52" s="799"/>
-      <c r="L52" s="799"/>
-      <c r="M52" s="800"/>
-      <c r="N52" s="801" t="s">
+      <c r="E52" s="800"/>
+      <c r="F52" s="800"/>
+      <c r="G52" s="800"/>
+      <c r="H52" s="800"/>
+      <c r="I52" s="800"/>
+      <c r="J52" s="800"/>
+      <c r="K52" s="800"/>
+      <c r="L52" s="800"/>
+      <c r="M52" s="801"/>
+      <c r="N52" s="802" t="s">
         <v>378</v>
       </c>
-      <c r="O52" s="801"/>
-      <c r="P52" s="801" t="s">
+      <c r="O52" s="802"/>
+      <c r="P52" s="802" t="s">
         <v>51</v>
       </c>
-      <c r="Q52" s="801"/>
+      <c r="Q52" s="802"/>
       <c r="R52" s="432"/>
       <c r="S52" s="377"/>
     </row>
     <row r="53" spans="2:21" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B53" s="376"/>
       <c r="C53" s="431"/>
-      <c r="D53" s="802"/>
-      <c r="E53" s="806"/>
-      <c r="F53" s="806"/>
-      <c r="G53" s="806"/>
-      <c r="H53" s="806"/>
-      <c r="I53" s="806"/>
-      <c r="J53" s="806"/>
-      <c r="K53" s="806"/>
-      <c r="L53" s="806"/>
-      <c r="M53" s="803"/>
-      <c r="N53" s="802" t="str">
+      <c r="D53" s="803"/>
+      <c r="E53" s="807"/>
+      <c r="F53" s="807"/>
+      <c r="G53" s="807"/>
+      <c r="H53" s="807"/>
+      <c r="I53" s="807"/>
+      <c r="J53" s="807"/>
+      <c r="K53" s="807"/>
+      <c r="L53" s="807"/>
+      <c r="M53" s="804"/>
+      <c r="N53" s="803" t="str">
         <f>IF(P53&gt;80,"Validé",IF(P53&lt;70,"Non Validé", "Validé avec réserve"))</f>
         <v>Non Validé</v>
       </c>
-      <c r="O53" s="803"/>
-      <c r="P53" s="804">
+      <c r="O53" s="804"/>
+      <c r="P53" s="805">
         <f>IF(SUM(P42:P51)&gt;100,100,SUM(P42:P51))</f>
         <v>0</v>
       </c>
-      <c r="Q53" s="805"/>
+      <c r="Q53" s="806"/>
       <c r="R53" s="432"/>
       <c r="S53" s="377"/>
     </row>
@@ -43398,126 +43401,126 @@
     </row>
     <row r="56" spans="2:21" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B56" s="376"/>
-      <c r="C56" s="767" t="s">
+      <c r="C56" s="768" t="s">
         <v>205</v>
       </c>
-      <c r="D56" s="768"/>
-      <c r="E56" s="768"/>
-      <c r="F56" s="768"/>
-      <c r="G56" s="768"/>
-      <c r="H56" s="768"/>
-      <c r="I56" s="768"/>
-      <c r="J56" s="768"/>
-      <c r="K56" s="768"/>
-      <c r="L56" s="768"/>
-      <c r="M56" s="768"/>
-      <c r="N56" s="768"/>
-      <c r="O56" s="768"/>
-      <c r="P56" s="768"/>
-      <c r="Q56" s="768"/>
-      <c r="R56" s="769"/>
+      <c r="D56" s="769"/>
+      <c r="E56" s="769"/>
+      <c r="F56" s="769"/>
+      <c r="G56" s="769"/>
+      <c r="H56" s="769"/>
+      <c r="I56" s="769"/>
+      <c r="J56" s="769"/>
+      <c r="K56" s="769"/>
+      <c r="L56" s="769"/>
+      <c r="M56" s="769"/>
+      <c r="N56" s="769"/>
+      <c r="O56" s="769"/>
+      <c r="P56" s="769"/>
+      <c r="Q56" s="769"/>
+      <c r="R56" s="770"/>
       <c r="S56" s="377"/>
     </row>
     <row r="57" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B57" s="376"/>
-      <c r="C57" s="789" t="s">
+      <c r="C57" s="790" t="s">
         <v>376</v>
       </c>
-      <c r="D57" s="790"/>
-      <c r="E57" s="790"/>
-      <c r="F57" s="790"/>
-      <c r="G57" s="790"/>
-      <c r="H57" s="790"/>
-      <c r="I57" s="790"/>
-      <c r="J57" s="790"/>
-      <c r="K57" s="790"/>
-      <c r="L57" s="790"/>
-      <c r="M57" s="790"/>
-      <c r="N57" s="790"/>
-      <c r="O57" s="790"/>
-      <c r="P57" s="790"/>
-      <c r="Q57" s="790"/>
-      <c r="R57" s="791"/>
+      <c r="D57" s="791"/>
+      <c r="E57" s="791"/>
+      <c r="F57" s="791"/>
+      <c r="G57" s="791"/>
+      <c r="H57" s="791"/>
+      <c r="I57" s="791"/>
+      <c r="J57" s="791"/>
+      <c r="K57" s="791"/>
+      <c r="L57" s="791"/>
+      <c r="M57" s="791"/>
+      <c r="N57" s="791"/>
+      <c r="O57" s="791"/>
+      <c r="P57" s="791"/>
+      <c r="Q57" s="791"/>
+      <c r="R57" s="792"/>
       <c r="S57" s="377"/>
     </row>
     <row r="58" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B58" s="376"/>
-      <c r="C58" s="792"/>
-      <c r="D58" s="790"/>
-      <c r="E58" s="790"/>
-      <c r="F58" s="790"/>
-      <c r="G58" s="790"/>
-      <c r="H58" s="790"/>
-      <c r="I58" s="790"/>
-      <c r="J58" s="790"/>
-      <c r="K58" s="790"/>
-      <c r="L58" s="790"/>
-      <c r="M58" s="790"/>
-      <c r="N58" s="790"/>
-      <c r="O58" s="790"/>
-      <c r="P58" s="790"/>
-      <c r="Q58" s="790"/>
-      <c r="R58" s="791"/>
+      <c r="C58" s="793"/>
+      <c r="D58" s="791"/>
+      <c r="E58" s="791"/>
+      <c r="F58" s="791"/>
+      <c r="G58" s="791"/>
+      <c r="H58" s="791"/>
+      <c r="I58" s="791"/>
+      <c r="J58" s="791"/>
+      <c r="K58" s="791"/>
+      <c r="L58" s="791"/>
+      <c r="M58" s="791"/>
+      <c r="N58" s="791"/>
+      <c r="O58" s="791"/>
+      <c r="P58" s="791"/>
+      <c r="Q58" s="791"/>
+      <c r="R58" s="792"/>
       <c r="S58" s="377"/>
     </row>
     <row r="59" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B59" s="376"/>
-      <c r="C59" s="792"/>
-      <c r="D59" s="790"/>
-      <c r="E59" s="790"/>
-      <c r="F59" s="790"/>
-      <c r="G59" s="790"/>
-      <c r="H59" s="790"/>
-      <c r="I59" s="790"/>
-      <c r="J59" s="790"/>
-      <c r="K59" s="790"/>
-      <c r="L59" s="790"/>
-      <c r="M59" s="790"/>
-      <c r="N59" s="790"/>
-      <c r="O59" s="790"/>
-      <c r="P59" s="790"/>
-      <c r="Q59" s="790"/>
-      <c r="R59" s="791"/>
+      <c r="C59" s="793"/>
+      <c r="D59" s="791"/>
+      <c r="E59" s="791"/>
+      <c r="F59" s="791"/>
+      <c r="G59" s="791"/>
+      <c r="H59" s="791"/>
+      <c r="I59" s="791"/>
+      <c r="J59" s="791"/>
+      <c r="K59" s="791"/>
+      <c r="L59" s="791"/>
+      <c r="M59" s="791"/>
+      <c r="N59" s="791"/>
+      <c r="O59" s="791"/>
+      <c r="P59" s="791"/>
+      <c r="Q59" s="791"/>
+      <c r="R59" s="792"/>
       <c r="S59" s="377"/>
     </row>
     <row r="60" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B60" s="376"/>
-      <c r="C60" s="792"/>
-      <c r="D60" s="790"/>
-      <c r="E60" s="790"/>
-      <c r="F60" s="790"/>
-      <c r="G60" s="790"/>
-      <c r="H60" s="790"/>
-      <c r="I60" s="790"/>
-      <c r="J60" s="790"/>
-      <c r="K60" s="790"/>
-      <c r="L60" s="790"/>
-      <c r="M60" s="790"/>
-      <c r="N60" s="790"/>
-      <c r="O60" s="790"/>
-      <c r="P60" s="790"/>
-      <c r="Q60" s="790"/>
-      <c r="R60" s="791"/>
+      <c r="C60" s="793"/>
+      <c r="D60" s="791"/>
+      <c r="E60" s="791"/>
+      <c r="F60" s="791"/>
+      <c r="G60" s="791"/>
+      <c r="H60" s="791"/>
+      <c r="I60" s="791"/>
+      <c r="J60" s="791"/>
+      <c r="K60" s="791"/>
+      <c r="L60" s="791"/>
+      <c r="M60" s="791"/>
+      <c r="N60" s="791"/>
+      <c r="O60" s="791"/>
+      <c r="P60" s="791"/>
+      <c r="Q60" s="791"/>
+      <c r="R60" s="792"/>
       <c r="S60" s="377"/>
     </row>
     <row r="61" spans="2:21" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B61" s="376"/>
-      <c r="C61" s="793"/>
-      <c r="D61" s="794"/>
-      <c r="E61" s="794"/>
-      <c r="F61" s="794"/>
-      <c r="G61" s="794"/>
-      <c r="H61" s="794"/>
-      <c r="I61" s="794"/>
-      <c r="J61" s="794"/>
-      <c r="K61" s="794"/>
-      <c r="L61" s="794"/>
-      <c r="M61" s="794"/>
-      <c r="N61" s="794"/>
-      <c r="O61" s="794"/>
-      <c r="P61" s="794"/>
-      <c r="Q61" s="794"/>
-      <c r="R61" s="795"/>
+      <c r="C61" s="794"/>
+      <c r="D61" s="795"/>
+      <c r="E61" s="795"/>
+      <c r="F61" s="795"/>
+      <c r="G61" s="795"/>
+      <c r="H61" s="795"/>
+      <c r="I61" s="795"/>
+      <c r="J61" s="795"/>
+      <c r="K61" s="795"/>
+      <c r="L61" s="795"/>
+      <c r="M61" s="795"/>
+      <c r="N61" s="795"/>
+      <c r="O61" s="795"/>
+      <c r="P61" s="795"/>
+      <c r="Q61" s="795"/>
+      <c r="R61" s="796"/>
       <c r="S61" s="377"/>
     </row>
     <row r="62" spans="2:21" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">

--- a/AutosurveillanceTemplates/Q_GRAV.xlsx
+++ b/AutosurveillanceTemplates/Q_GRAV.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndhuy\AppData\Roaming\Microsoft\AddIns\AutosurveillanceTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A970B4-056D-46AE-B91C-11728CC78D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBCBE09-2F52-4C32-AB27-C124A4AF1913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="302">
   <si>
     <t>Code</t>
   </si>
@@ -1996,9 +1996,6 @@
   </si>
   <si>
     <t>question 8</t>
-  </si>
-  <si>
-    <t>les formules en Q sont à vérifier</t>
   </si>
 </sst>
 </file>
@@ -4002,6 +3999,114 @@
     <xf numFmtId="10" fontId="28" fillId="13" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4011,11 +4116,86 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4029,24 +4209,6 @@
     <xf numFmtId="0" fontId="30" fillId="20" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4056,12 +4218,6 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4070,165 +4226,6 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4804,54 +4801,54 @@
     </row>
     <row r="2" spans="2:28" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B2" s="110"/>
-      <c r="C2" s="197" t="s">
+      <c r="C2" s="258" t="s">
         <v>233</v>
       </c>
-      <c r="D2" s="198"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="198"/>
-      <c r="G2" s="198"/>
-      <c r="H2" s="198"/>
-      <c r="I2" s="198"/>
-      <c r="J2" s="198"/>
-      <c r="K2" s="198"/>
-      <c r="L2" s="198"/>
-      <c r="M2" s="198"/>
-      <c r="N2" s="198"/>
-      <c r="O2" s="198"/>
-      <c r="P2" s="198"/>
-      <c r="Q2" s="198"/>
-      <c r="R2" s="198"/>
-      <c r="S2" s="198"/>
-      <c r="T2" s="199"/>
+      <c r="D2" s="259"/>
+      <c r="E2" s="259"/>
+      <c r="F2" s="259"/>
+      <c r="G2" s="259"/>
+      <c r="H2" s="259"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="259"/>
+      <c r="K2" s="259"/>
+      <c r="L2" s="259"/>
+      <c r="M2" s="259"/>
+      <c r="N2" s="259"/>
+      <c r="O2" s="259"/>
+      <c r="P2" s="259"/>
+      <c r="Q2" s="259"/>
+      <c r="R2" s="259"/>
+      <c r="S2" s="259"/>
+      <c r="T2" s="260"/>
       <c r="U2" s="112"/>
     </row>
     <row r="3" spans="2:28" s="97" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="111"/>
-      <c r="C3" s="211" t="s">
+      <c r="C3" s="252" t="s">
         <v>268</v>
       </c>
-      <c r="D3" s="211"/>
-      <c r="E3" s="217"/>
-      <c r="F3" s="217"/>
-      <c r="G3" s="217"/>
-      <c r="H3" s="219" t="s">
+      <c r="D3" s="252"/>
+      <c r="E3" s="231"/>
+      <c r="F3" s="231"/>
+      <c r="G3" s="231"/>
+      <c r="H3" s="250" t="s">
         <v>237</v>
       </c>
-      <c r="I3" s="219"/>
-      <c r="J3" s="219"/>
-      <c r="K3" s="217"/>
-      <c r="L3" s="217"/>
-      <c r="M3" s="217"/>
-      <c r="N3" s="217"/>
-      <c r="O3" s="211" t="s">
+      <c r="I3" s="250"/>
+      <c r="J3" s="250"/>
+      <c r="K3" s="231"/>
+      <c r="L3" s="231"/>
+      <c r="M3" s="231"/>
+      <c r="N3" s="231"/>
+      <c r="O3" s="252" t="s">
         <v>238</v>
       </c>
-      <c r="P3" s="211"/>
-      <c r="Q3" s="211"/>
-      <c r="R3" s="217"/>
-      <c r="S3" s="217"/>
-      <c r="T3" s="226"/>
+      <c r="P3" s="252"/>
+      <c r="Q3" s="252"/>
+      <c r="R3" s="231"/>
+      <c r="S3" s="231"/>
+      <c r="T3" s="232"/>
       <c r="U3" s="113"/>
       <c r="V3" s="137"/>
       <c r="W3" s="137"/>
@@ -4863,30 +4860,30 @@
     </row>
     <row r="4" spans="2:28" s="97" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="111"/>
-      <c r="C4" s="211" t="s">
+      <c r="C4" s="252" t="s">
         <v>234</v>
       </c>
-      <c r="D4" s="211"/>
-      <c r="E4" s="217"/>
-      <c r="F4" s="217"/>
-      <c r="G4" s="217"/>
-      <c r="H4" s="240" t="s">
+      <c r="D4" s="252"/>
+      <c r="E4" s="231"/>
+      <c r="F4" s="231"/>
+      <c r="G4" s="231"/>
+      <c r="H4" s="251" t="s">
         <v>293</v>
       </c>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="217"/>
-      <c r="L4" s="217"/>
-      <c r="M4" s="217"/>
-      <c r="N4" s="217"/>
-      <c r="O4" s="211" t="s">
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="231"/>
+      <c r="L4" s="231"/>
+      <c r="M4" s="231"/>
+      <c r="N4" s="231"/>
+      <c r="O4" s="252" t="s">
         <v>289</v>
       </c>
-      <c r="P4" s="211"/>
-      <c r="Q4" s="211"/>
-      <c r="R4" s="217"/>
-      <c r="S4" s="217"/>
-      <c r="T4" s="226"/>
+      <c r="P4" s="252"/>
+      <c r="Q4" s="252"/>
+      <c r="R4" s="231"/>
+      <c r="S4" s="231"/>
+      <c r="T4" s="232"/>
       <c r="U4" s="113"/>
       <c r="V4" s="137"/>
       <c r="W4" s="137"/>
@@ -4898,30 +4895,30 @@
     </row>
     <row r="5" spans="2:28" s="97" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="111"/>
-      <c r="C5" s="211" t="s">
+      <c r="C5" s="252" t="s">
         <v>235</v>
       </c>
-      <c r="D5" s="211"/>
-      <c r="E5" s="217"/>
-      <c r="F5" s="217"/>
-      <c r="G5" s="217"/>
-      <c r="H5" s="219" t="s">
+      <c r="D5" s="252"/>
+      <c r="E5" s="231"/>
+      <c r="F5" s="231"/>
+      <c r="G5" s="231"/>
+      <c r="H5" s="250" t="s">
         <v>272</v>
       </c>
-      <c r="I5" s="219"/>
-      <c r="J5" s="219"/>
-      <c r="K5" s="217"/>
-      <c r="L5" s="217"/>
-      <c r="M5" s="217"/>
-      <c r="N5" s="217"/>
-      <c r="O5" s="211" t="s">
+      <c r="I5" s="250"/>
+      <c r="J5" s="250"/>
+      <c r="K5" s="231"/>
+      <c r="L5" s="231"/>
+      <c r="M5" s="231"/>
+      <c r="N5" s="231"/>
+      <c r="O5" s="252" t="s">
         <v>281</v>
       </c>
-      <c r="P5" s="211"/>
-      <c r="Q5" s="211"/>
-      <c r="R5" s="227"/>
-      <c r="S5" s="227"/>
-      <c r="T5" s="228"/>
+      <c r="P5" s="252"/>
+      <c r="Q5" s="252"/>
+      <c r="R5" s="233"/>
+      <c r="S5" s="233"/>
+      <c r="T5" s="234"/>
       <c r="U5" s="113"/>
       <c r="V5" s="137"/>
       <c r="W5" s="137"/>
@@ -4933,33 +4930,33 @@
     </row>
     <row r="6" spans="2:28" s="97" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="111"/>
-      <c r="C6" s="216" t="s">
+      <c r="C6" s="253" t="s">
         <v>236</v>
       </c>
-      <c r="D6" s="216"/>
-      <c r="E6" s="218"/>
-      <c r="F6" s="218"/>
-      <c r="G6" s="218"/>
-      <c r="H6" s="220" t="s">
+      <c r="D6" s="253"/>
+      <c r="E6" s="249"/>
+      <c r="F6" s="249"/>
+      <c r="G6" s="249"/>
+      <c r="H6" s="254" t="s">
         <v>294</v>
       </c>
-      <c r="I6" s="220"/>
-      <c r="J6" s="220"/>
-      <c r="K6" s="218" t="str">
+      <c r="I6" s="254"/>
+      <c r="J6" s="254"/>
+      <c r="K6" s="249" t="str">
         <f>D40</f>
         <v>Canal Venturi</v>
       </c>
-      <c r="L6" s="218"/>
-      <c r="M6" s="218"/>
-      <c r="N6" s="218"/>
-      <c r="O6" s="216" t="s">
+      <c r="L6" s="249"/>
+      <c r="M6" s="249"/>
+      <c r="N6" s="249"/>
+      <c r="O6" s="253" t="s">
         <v>280</v>
       </c>
-      <c r="P6" s="216"/>
-      <c r="Q6" s="216"/>
-      <c r="R6" s="229"/>
-      <c r="S6" s="229"/>
-      <c r="T6" s="230"/>
+      <c r="P6" s="253"/>
+      <c r="Q6" s="253"/>
+      <c r="R6" s="235"/>
+      <c r="S6" s="235"/>
+      <c r="T6" s="236"/>
       <c r="U6" s="113"/>
       <c r="V6" s="137"/>
       <c r="W6" s="137"/>
@@ -5000,26 +4997,26 @@
     </row>
     <row r="8" spans="2:28" s="96" customFormat="1" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="103"/>
-      <c r="C8" s="231" t="s">
+      <c r="C8" s="197" t="s">
         <v>250</v>
       </c>
-      <c r="D8" s="232"/>
-      <c r="E8" s="232"/>
-      <c r="F8" s="232"/>
-      <c r="G8" s="232"/>
-      <c r="H8" s="232"/>
-      <c r="I8" s="232"/>
-      <c r="J8" s="232"/>
-      <c r="K8" s="232"/>
-      <c r="L8" s="232"/>
-      <c r="M8" s="232"/>
-      <c r="N8" s="232"/>
-      <c r="O8" s="232"/>
-      <c r="P8" s="232"/>
-      <c r="Q8" s="232"/>
-      <c r="R8" s="232"/>
-      <c r="S8" s="232"/>
-      <c r="T8" s="233"/>
+      <c r="D8" s="198"/>
+      <c r="E8" s="198"/>
+      <c r="F8" s="198"/>
+      <c r="G8" s="198"/>
+      <c r="H8" s="198"/>
+      <c r="I8" s="198"/>
+      <c r="J8" s="198"/>
+      <c r="K8" s="198"/>
+      <c r="L8" s="198"/>
+      <c r="M8" s="198"/>
+      <c r="N8" s="198"/>
+      <c r="O8" s="198"/>
+      <c r="P8" s="198"/>
+      <c r="Q8" s="198"/>
+      <c r="R8" s="198"/>
+      <c r="S8" s="198"/>
+      <c r="T8" s="199"/>
       <c r="U8" s="104"/>
       <c r="V8" s="138"/>
       <c r="W8" s="138"/>
@@ -5061,76 +5058,76 @@
     <row r="10" spans="2:28" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B10" s="105"/>
       <c r="C10" s="149"/>
-      <c r="D10" s="234" t="s">
+      <c r="D10" s="237" t="s">
         <v>270</v>
       </c>
-      <c r="E10" s="235"/>
-      <c r="F10" s="235"/>
-      <c r="G10" s="235"/>
-      <c r="H10" s="235"/>
-      <c r="I10" s="235"/>
-      <c r="J10" s="235"/>
-      <c r="K10" s="235"/>
-      <c r="L10" s="235"/>
-      <c r="M10" s="235"/>
-      <c r="N10" s="235"/>
-      <c r="O10" s="235"/>
-      <c r="P10" s="235"/>
-      <c r="Q10" s="235"/>
-      <c r="R10" s="235"/>
-      <c r="S10" s="236"/>
+      <c r="E10" s="238"/>
+      <c r="F10" s="238"/>
+      <c r="G10" s="238"/>
+      <c r="H10" s="238"/>
+      <c r="I10" s="238"/>
+      <c r="J10" s="238"/>
+      <c r="K10" s="238"/>
+      <c r="L10" s="238"/>
+      <c r="M10" s="238"/>
+      <c r="N10" s="238"/>
+      <c r="O10" s="238"/>
+      <c r="P10" s="238"/>
+      <c r="Q10" s="238"/>
+      <c r="R10" s="238"/>
+      <c r="S10" s="239"/>
       <c r="T10" s="150"/>
       <c r="U10" s="106"/>
     </row>
     <row r="11" spans="2:28" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B11" s="105"/>
       <c r="C11" s="151"/>
-      <c r="D11" s="201" t="s">
+      <c r="D11" s="240" t="s">
         <v>241</v>
       </c>
-      <c r="E11" s="202"/>
-      <c r="F11" s="203"/>
-      <c r="G11" s="237"/>
-      <c r="H11" s="238"/>
-      <c r="I11" s="238"/>
-      <c r="J11" s="238"/>
-      <c r="K11" s="239"/>
-      <c r="L11" s="201" t="s">
+      <c r="E11" s="241"/>
+      <c r="F11" s="242"/>
+      <c r="G11" s="246"/>
+      <c r="H11" s="247"/>
+      <c r="I11" s="247"/>
+      <c r="J11" s="247"/>
+      <c r="K11" s="248"/>
+      <c r="L11" s="240" t="s">
         <v>244</v>
       </c>
-      <c r="M11" s="202"/>
-      <c r="N11" s="202"/>
-      <c r="O11" s="203"/>
-      <c r="P11" s="204"/>
-      <c r="Q11" s="205"/>
-      <c r="R11" s="205"/>
-      <c r="S11" s="206"/>
+      <c r="M11" s="241"/>
+      <c r="N11" s="241"/>
+      <c r="O11" s="242"/>
+      <c r="P11" s="243"/>
+      <c r="Q11" s="244"/>
+      <c r="R11" s="244"/>
+      <c r="S11" s="245"/>
       <c r="T11" s="152"/>
       <c r="U11" s="106"/>
     </row>
     <row r="12" spans="2:28" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B12" s="105"/>
       <c r="C12" s="151"/>
-      <c r="D12" s="201" t="s">
+      <c r="D12" s="240" t="s">
         <v>242</v>
       </c>
-      <c r="E12" s="202"/>
-      <c r="F12" s="203"/>
-      <c r="G12" s="204"/>
-      <c r="H12" s="205"/>
-      <c r="I12" s="205"/>
-      <c r="J12" s="205"/>
-      <c r="K12" s="206"/>
-      <c r="L12" s="201" t="s">
+      <c r="E12" s="241"/>
+      <c r="F12" s="242"/>
+      <c r="G12" s="243"/>
+      <c r="H12" s="244"/>
+      <c r="I12" s="244"/>
+      <c r="J12" s="244"/>
+      <c r="K12" s="245"/>
+      <c r="L12" s="240" t="s">
         <v>245</v>
       </c>
-      <c r="M12" s="202"/>
-      <c r="N12" s="202"/>
-      <c r="O12" s="203"/>
-      <c r="P12" s="204"/>
-      <c r="Q12" s="205"/>
-      <c r="R12" s="205"/>
-      <c r="S12" s="206"/>
+      <c r="M12" s="241"/>
+      <c r="N12" s="241"/>
+      <c r="O12" s="242"/>
+      <c r="P12" s="243"/>
+      <c r="Q12" s="244"/>
+      <c r="R12" s="244"/>
+      <c r="S12" s="245"/>
       <c r="T12" s="152"/>
       <c r="U12" s="106"/>
       <c r="X12" s="141"/>
@@ -5139,78 +5136,78 @@
     <row r="13" spans="2:28" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B13" s="105"/>
       <c r="C13" s="151"/>
-      <c r="D13" s="201" t="s">
+      <c r="D13" s="240" t="s">
         <v>239</v>
       </c>
-      <c r="E13" s="202"/>
-      <c r="F13" s="203"/>
-      <c r="G13" s="204"/>
-      <c r="H13" s="205"/>
-      <c r="I13" s="205"/>
-      <c r="J13" s="205"/>
-      <c r="K13" s="206"/>
-      <c r="L13" s="215" t="s">
+      <c r="E13" s="241"/>
+      <c r="F13" s="242"/>
+      <c r="G13" s="243"/>
+      <c r="H13" s="244"/>
+      <c r="I13" s="244"/>
+      <c r="J13" s="244"/>
+      <c r="K13" s="245"/>
+      <c r="L13" s="257" t="s">
         <v>265</v>
       </c>
-      <c r="M13" s="215"/>
-      <c r="N13" s="215"/>
-      <c r="O13" s="215"/>
-      <c r="P13" s="210"/>
-      <c r="Q13" s="210"/>
-      <c r="R13" s="210"/>
-      <c r="S13" s="210"/>
+      <c r="M13" s="257"/>
+      <c r="N13" s="257"/>
+      <c r="O13" s="257"/>
+      <c r="P13" s="196"/>
+      <c r="Q13" s="196"/>
+      <c r="R13" s="196"/>
+      <c r="S13" s="196"/>
       <c r="T13" s="152"/>
       <c r="U13" s="106"/>
     </row>
     <row r="14" spans="2:28" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B14" s="105"/>
       <c r="C14" s="151"/>
-      <c r="D14" s="201" t="s">
+      <c r="D14" s="240" t="s">
         <v>240</v>
       </c>
-      <c r="E14" s="202"/>
-      <c r="F14" s="203"/>
-      <c r="G14" s="210"/>
-      <c r="H14" s="210"/>
-      <c r="I14" s="210"/>
-      <c r="J14" s="210"/>
-      <c r="K14" s="210"/>
-      <c r="L14" s="215" t="s">
+      <c r="E14" s="241"/>
+      <c r="F14" s="242"/>
+      <c r="G14" s="196"/>
+      <c r="H14" s="196"/>
+      <c r="I14" s="196"/>
+      <c r="J14" s="196"/>
+      <c r="K14" s="196"/>
+      <c r="L14" s="257" t="s">
         <v>288</v>
       </c>
-      <c r="M14" s="215"/>
-      <c r="N14" s="215"/>
-      <c r="O14" s="215"/>
-      <c r="P14" s="210"/>
-      <c r="Q14" s="210"/>
-      <c r="R14" s="210"/>
-      <c r="S14" s="210"/>
+      <c r="M14" s="257"/>
+      <c r="N14" s="257"/>
+      <c r="O14" s="257"/>
+      <c r="P14" s="196"/>
+      <c r="Q14" s="196"/>
+      <c r="R14" s="196"/>
+      <c r="S14" s="196"/>
       <c r="T14" s="152"/>
       <c r="U14" s="106"/>
     </row>
     <row r="15" spans="2:28" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B15" s="105"/>
       <c r="C15" s="151"/>
-      <c r="D15" s="201" t="s">
+      <c r="D15" s="240" t="s">
         <v>243</v>
       </c>
-      <c r="E15" s="202"/>
-      <c r="F15" s="203"/>
-      <c r="G15" s="210"/>
-      <c r="H15" s="210"/>
-      <c r="I15" s="210"/>
-      <c r="J15" s="210"/>
-      <c r="K15" s="210"/>
-      <c r="L15" s="215" t="s">
+      <c r="E15" s="241"/>
+      <c r="F15" s="242"/>
+      <c r="G15" s="196"/>
+      <c r="H15" s="196"/>
+      <c r="I15" s="196"/>
+      <c r="J15" s="196"/>
+      <c r="K15" s="196"/>
+      <c r="L15" s="257" t="s">
         <v>295</v>
       </c>
-      <c r="M15" s="215"/>
-      <c r="N15" s="215"/>
-      <c r="O15" s="215"/>
-      <c r="P15" s="260"/>
-      <c r="Q15" s="260"/>
-      <c r="R15" s="260"/>
-      <c r="S15" s="260"/>
+      <c r="M15" s="257"/>
+      <c r="N15" s="257"/>
+      <c r="O15" s="257"/>
+      <c r="P15" s="192"/>
+      <c r="Q15" s="192"/>
+      <c r="R15" s="192"/>
+      <c r="S15" s="192"/>
       <c r="T15" s="152"/>
       <c r="U15" s="106"/>
     </row>
@@ -5261,128 +5258,128 @@
     <row r="18" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B18" s="105"/>
       <c r="C18" s="151"/>
-      <c r="D18" s="207" t="s">
+      <c r="D18" s="262" t="s">
         <v>247</v>
       </c>
-      <c r="E18" s="207"/>
-      <c r="F18" s="207"/>
-      <c r="G18" s="209" t="s">
+      <c r="E18" s="262"/>
+      <c r="F18" s="262"/>
+      <c r="G18" s="264" t="s">
         <v>262</v>
       </c>
-      <c r="H18" s="209"/>
-      <c r="I18" s="209"/>
-      <c r="J18" s="209"/>
-      <c r="K18" s="209"/>
-      <c r="L18" s="209"/>
-      <c r="M18" s="209"/>
-      <c r="N18" s="209"/>
-      <c r="O18" s="209"/>
-      <c r="P18" s="209"/>
-      <c r="Q18" s="209"/>
-      <c r="R18" s="209"/>
-      <c r="S18" s="209"/>
+      <c r="H18" s="264"/>
+      <c r="I18" s="264"/>
+      <c r="J18" s="264"/>
+      <c r="K18" s="264"/>
+      <c r="L18" s="264"/>
+      <c r="M18" s="264"/>
+      <c r="N18" s="264"/>
+      <c r="O18" s="264"/>
+      <c r="P18" s="264"/>
+      <c r="Q18" s="264"/>
+      <c r="R18" s="264"/>
+      <c r="S18" s="264"/>
       <c r="T18" s="152"/>
       <c r="U18" s="106"/>
     </row>
     <row r="19" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B19" s="105"/>
       <c r="C19" s="151"/>
-      <c r="D19" s="208" t="s">
+      <c r="D19" s="263" t="s">
         <v>271</v>
       </c>
-      <c r="E19" s="208"/>
-      <c r="F19" s="208"/>
-      <c r="G19" s="208"/>
-      <c r="H19" s="208"/>
-      <c r="I19" s="208"/>
-      <c r="J19" s="208"/>
-      <c r="K19" s="208"/>
-      <c r="L19" s="208"/>
-      <c r="M19" s="208"/>
-      <c r="N19" s="208"/>
-      <c r="O19" s="208"/>
-      <c r="P19" s="208"/>
-      <c r="Q19" s="208"/>
-      <c r="R19" s="208"/>
-      <c r="S19" s="208"/>
+      <c r="E19" s="263"/>
+      <c r="F19" s="263"/>
+      <c r="G19" s="263"/>
+      <c r="H19" s="263"/>
+      <c r="I19" s="263"/>
+      <c r="J19" s="263"/>
+      <c r="K19" s="263"/>
+      <c r="L19" s="263"/>
+      <c r="M19" s="263"/>
+      <c r="N19" s="263"/>
+      <c r="O19" s="263"/>
+      <c r="P19" s="263"/>
+      <c r="Q19" s="263"/>
+      <c r="R19" s="263"/>
+      <c r="S19" s="263"/>
       <c r="T19" s="152"/>
       <c r="U19" s="106"/>
     </row>
     <row r="20" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B20" s="105"/>
       <c r="C20" s="151"/>
-      <c r="D20" s="201" t="s">
+      <c r="D20" s="240" t="s">
         <v>210</v>
       </c>
-      <c r="E20" s="202"/>
-      <c r="F20" s="203"/>
-      <c r="G20" s="204"/>
-      <c r="H20" s="205"/>
-      <c r="I20" s="205"/>
-      <c r="J20" s="205"/>
-      <c r="K20" s="206"/>
-      <c r="L20" s="201" t="s">
+      <c r="E20" s="241"/>
+      <c r="F20" s="242"/>
+      <c r="G20" s="243"/>
+      <c r="H20" s="244"/>
+      <c r="I20" s="244"/>
+      <c r="J20" s="244"/>
+      <c r="K20" s="245"/>
+      <c r="L20" s="240" t="s">
         <v>85</v>
       </c>
-      <c r="M20" s="202"/>
-      <c r="N20" s="202"/>
-      <c r="O20" s="203"/>
-      <c r="P20" s="204"/>
-      <c r="Q20" s="205"/>
-      <c r="R20" s="205"/>
-      <c r="S20" s="206"/>
+      <c r="M20" s="241"/>
+      <c r="N20" s="241"/>
+      <c r="O20" s="242"/>
+      <c r="P20" s="243"/>
+      <c r="Q20" s="244"/>
+      <c r="R20" s="244"/>
+      <c r="S20" s="245"/>
       <c r="T20" s="152"/>
       <c r="U20" s="106"/>
     </row>
     <row r="21" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B21" s="105"/>
       <c r="C21" s="151"/>
-      <c r="D21" s="201" t="s">
+      <c r="D21" s="240" t="s">
         <v>211</v>
       </c>
-      <c r="E21" s="202"/>
-      <c r="F21" s="203"/>
-      <c r="G21" s="204"/>
-      <c r="H21" s="205"/>
-      <c r="I21" s="205"/>
-      <c r="J21" s="205"/>
-      <c r="K21" s="206"/>
-      <c r="L21" s="201" t="s">
+      <c r="E21" s="241"/>
+      <c r="F21" s="242"/>
+      <c r="G21" s="243"/>
+      <c r="H21" s="244"/>
+      <c r="I21" s="244"/>
+      <c r="J21" s="244"/>
+      <c r="K21" s="245"/>
+      <c r="L21" s="240" t="s">
         <v>86</v>
       </c>
-      <c r="M21" s="202"/>
-      <c r="N21" s="202"/>
-      <c r="O21" s="203"/>
-      <c r="P21" s="204"/>
-      <c r="Q21" s="205"/>
-      <c r="R21" s="205"/>
-      <c r="S21" s="206"/>
+      <c r="M21" s="241"/>
+      <c r="N21" s="241"/>
+      <c r="O21" s="242"/>
+      <c r="P21" s="243"/>
+      <c r="Q21" s="244"/>
+      <c r="R21" s="244"/>
+      <c r="S21" s="245"/>
       <c r="T21" s="152"/>
       <c r="U21" s="106"/>
     </row>
     <row r="22" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B22" s="105"/>
       <c r="C22" s="151"/>
-      <c r="D22" s="201" t="s">
+      <c r="D22" s="240" t="s">
         <v>212</v>
       </c>
-      <c r="E22" s="202"/>
-      <c r="F22" s="203"/>
-      <c r="G22" s="204"/>
-      <c r="H22" s="205"/>
-      <c r="I22" s="205"/>
-      <c r="J22" s="205"/>
-      <c r="K22" s="206"/>
-      <c r="L22" s="201" t="s">
+      <c r="E22" s="241"/>
+      <c r="F22" s="242"/>
+      <c r="G22" s="243"/>
+      <c r="H22" s="244"/>
+      <c r="I22" s="244"/>
+      <c r="J22" s="244"/>
+      <c r="K22" s="245"/>
+      <c r="L22" s="240" t="s">
         <v>246</v>
       </c>
-      <c r="M22" s="202"/>
-      <c r="N22" s="202"/>
-      <c r="O22" s="203"/>
-      <c r="P22" s="204"/>
-      <c r="Q22" s="205"/>
-      <c r="R22" s="205"/>
-      <c r="S22" s="206"/>
+      <c r="M22" s="241"/>
+      <c r="N22" s="241"/>
+      <c r="O22" s="242"/>
+      <c r="P22" s="243"/>
+      <c r="Q22" s="244"/>
+      <c r="R22" s="244"/>
+      <c r="S22" s="245"/>
       <c r="T22" s="152"/>
       <c r="U22" s="106"/>
     </row>
@@ -5411,22 +5408,22 @@
     <row r="24" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B24" s="105"/>
       <c r="C24" s="151"/>
-      <c r="D24" s="212" t="s">
+      <c r="D24" s="265" t="s">
         <v>249</v>
       </c>
-      <c r="E24" s="213"/>
-      <c r="F24" s="213"/>
-      <c r="G24" s="213"/>
-      <c r="H24" s="213"/>
-      <c r="I24" s="213"/>
-      <c r="J24" s="213"/>
-      <c r="K24" s="213"/>
-      <c r="L24" s="213"/>
-      <c r="M24" s="213"/>
-      <c r="N24" s="213"/>
-      <c r="O24" s="213"/>
-      <c r="P24" s="213"/>
-      <c r="Q24" s="214"/>
+      <c r="E24" s="266"/>
+      <c r="F24" s="266"/>
+      <c r="G24" s="266"/>
+      <c r="H24" s="266"/>
+      <c r="I24" s="266"/>
+      <c r="J24" s="266"/>
+      <c r="K24" s="266"/>
+      <c r="L24" s="266"/>
+      <c r="M24" s="266"/>
+      <c r="N24" s="266"/>
+      <c r="O24" s="266"/>
+      <c r="P24" s="266"/>
+      <c r="Q24" s="267"/>
       <c r="R24" s="182"/>
       <c r="S24" s="182"/>
       <c r="T24" s="152"/>
@@ -5435,26 +5432,26 @@
     <row r="25" spans="2:25" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B25" s="105"/>
       <c r="C25" s="151"/>
-      <c r="D25" s="200" t="s">
+      <c r="D25" s="261" t="s">
         <v>254</v>
       </c>
-      <c r="E25" s="200"/>
-      <c r="F25" s="200"/>
-      <c r="G25" s="200"/>
-      <c r="H25" s="261" t="s">
+      <c r="E25" s="261"/>
+      <c r="F25" s="261"/>
+      <c r="G25" s="261"/>
+      <c r="H25" s="193" t="s">
         <v>251</v>
       </c>
-      <c r="I25" s="262"/>
-      <c r="J25" s="262"/>
-      <c r="K25" s="262"/>
-      <c r="L25" s="262"/>
-      <c r="M25" s="263"/>
-      <c r="N25" s="200" t="s">
+      <c r="I25" s="194"/>
+      <c r="J25" s="194"/>
+      <c r="K25" s="194"/>
+      <c r="L25" s="194"/>
+      <c r="M25" s="195"/>
+      <c r="N25" s="261" t="s">
         <v>252</v>
       </c>
-      <c r="O25" s="200"/>
-      <c r="P25" s="200"/>
-      <c r="Q25" s="200"/>
+      <c r="O25" s="261"/>
+      <c r="P25" s="261"/>
+      <c r="Q25" s="261"/>
       <c r="R25" s="182"/>
       <c r="S25" s="182"/>
       <c r="T25" s="152"/>
@@ -5554,7 +5551,7 @@
         <v/>
       </c>
       <c r="Q27" s="175" t="str">
-        <f>IF($G$18&lt;&gt;"Mesure en parallèle",IF(OR(F27="",O27="",D27=0),IF(D27=0,"-",""),(O27-AVERAGE(O27,F27))/AVERAGE(O27,F27)),IF(OR(F27="",O27="",H27=""),IF(H27="","-",""),(O27-AVERAGE(O27,H27))/AVERAGE(O27,H27)))</f>
+        <f>IF($G$18&lt;&gt;"Mesure en parallèle",IF(OR(F27="",J27="",D27=0),IF(D27=0,"-",""),(J27-AVERAGE(J27,F27))/AVERAGE(J27,F27)),IF(OR(O27="",H27=""),IF(H27="","-",""),(J27-AVERAGE(O27,J27))/AVERAGE(O27,J27)))</f>
         <v>-</v>
       </c>
       <c r="R27" s="182"/>
@@ -5609,7 +5606,7 @@
         <v/>
       </c>
       <c r="Q28" s="175" t="str">
-        <f t="shared" ref="Q28:Q30" si="4">IF($G$18&lt;&gt;"Mesure en parallèle",IF(OR(F28="",O28="",D28=0),IF(D28=0,"-",""),(O28-AVERAGE(O28,F28))/AVERAGE(O28,F28)),IF(OR(F28="",O28="",H28=""),IF(H28="","-",""),(O28-AVERAGE(O28,H28))/AVERAGE(O28,H28)))</f>
+        <f t="shared" ref="Q28:Q30" si="4">IF($G$18&lt;&gt;"Mesure en parallèle",IF(OR(F28="",J28="",D28=0),IF(D28=0,"-",""),(J28-AVERAGE(J28,F28))/AVERAGE(J28,F28)),IF(OR(O28="",H28=""),IF(H28="","-",""),(J28-AVERAGE(O28,J28))/AVERAGE(O28,J28)))</f>
         <v>-</v>
       </c>
       <c r="R28" s="182"/>
@@ -5718,7 +5715,7 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q30" s="172" t="str">
+      <c r="Q30" s="175" t="str">
         <f t="shared" si="4"/>
         <v>-</v>
       </c>
@@ -5755,9 +5752,7 @@
       <c r="N31" s="114"/>
       <c r="O31" s="114"/>
       <c r="P31" s="114"/>
-      <c r="Q31" s="170" t="s">
-        <v>302</v>
-      </c>
+      <c r="Q31" s="170"/>
       <c r="R31" s="182"/>
       <c r="S31" s="182"/>
       <c r="T31" s="152"/>
@@ -5808,31 +5803,31 @@
     <row r="33" spans="2:28" s="117" customFormat="1" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B33" s="115"/>
       <c r="C33" s="154"/>
-      <c r="D33" s="221" t="s">
+      <c r="D33" s="255" t="s">
         <v>286</v>
       </c>
-      <c r="E33" s="222"/>
+      <c r="E33" s="256"/>
       <c r="F33" s="174" t="s">
         <v>248</v>
       </c>
-      <c r="G33" s="221" t="s">
+      <c r="G33" s="255" t="s">
         <v>251</v>
       </c>
-      <c r="H33" s="222"/>
-      <c r="I33" s="221" t="s">
+      <c r="H33" s="256"/>
+      <c r="I33" s="255" t="s">
         <v>287</v>
       </c>
-      <c r="J33" s="222"/>
-      <c r="K33" s="223" t="s">
+      <c r="J33" s="256"/>
+      <c r="K33" s="204" t="s">
         <v>263</v>
       </c>
-      <c r="L33" s="224"/>
-      <c r="M33" s="225"/>
-      <c r="N33" s="223" t="s">
+      <c r="L33" s="205"/>
+      <c r="M33" s="206"/>
+      <c r="N33" s="204" t="s">
         <v>264</v>
       </c>
-      <c r="O33" s="224"/>
-      <c r="P33" s="225"/>
+      <c r="O33" s="205"/>
+      <c r="P33" s="206"/>
       <c r="Q33" s="130"/>
       <c r="R33" s="182"/>
       <c r="S33" s="183"/>
@@ -5864,10 +5859,10 @@
       <c r="H34" s="144" t="s">
         <v>277</v>
       </c>
-      <c r="I34" s="266" t="s">
+      <c r="I34" s="202" t="s">
         <v>283</v>
       </c>
-      <c r="J34" s="267"/>
+      <c r="J34" s="203"/>
       <c r="K34" s="123" t="s">
         <v>255</v>
       </c>
@@ -5910,8 +5905,8 @@
       </c>
       <c r="G35" s="126"/>
       <c r="H35" s="131"/>
-      <c r="I35" s="264"/>
-      <c r="J35" s="265"/>
+      <c r="I35" s="200"/>
+      <c r="J35" s="201"/>
       <c r="K35" s="128" t="str">
         <f>IF(AND(E35&lt;&gt;"",G35&lt;&gt;"",G18&lt;&gt;"Mesure en parallèle"),(E35+G35)/2,IF(AND(I35&lt;&gt;"",G35&lt;&gt;"",G18="Mesure en parallèle"),(I35+G35)/2,""))</f>
         <v/>
@@ -6000,26 +5995,26 @@
     </row>
     <row r="38" spans="2:28" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B38" s="105"/>
-      <c r="C38" s="231" t="s">
+      <c r="C38" s="197" t="s">
         <v>257</v>
       </c>
-      <c r="D38" s="232"/>
-      <c r="E38" s="232"/>
-      <c r="F38" s="232"/>
-      <c r="G38" s="232"/>
-      <c r="H38" s="232"/>
-      <c r="I38" s="232"/>
-      <c r="J38" s="232"/>
-      <c r="K38" s="232"/>
-      <c r="L38" s="232"/>
-      <c r="M38" s="232"/>
-      <c r="N38" s="232"/>
-      <c r="O38" s="232"/>
-      <c r="P38" s="232"/>
-      <c r="Q38" s="232"/>
-      <c r="R38" s="232"/>
-      <c r="S38" s="232"/>
-      <c r="T38" s="233"/>
+      <c r="D38" s="198"/>
+      <c r="E38" s="198"/>
+      <c r="F38" s="198"/>
+      <c r="G38" s="198"/>
+      <c r="H38" s="198"/>
+      <c r="I38" s="198"/>
+      <c r="J38" s="198"/>
+      <c r="K38" s="198"/>
+      <c r="L38" s="198"/>
+      <c r="M38" s="198"/>
+      <c r="N38" s="198"/>
+      <c r="O38" s="198"/>
+      <c r="P38" s="198"/>
+      <c r="Q38" s="198"/>
+      <c r="R38" s="198"/>
+      <c r="S38" s="198"/>
+      <c r="T38" s="199"/>
       <c r="U38" s="106"/>
     </row>
     <row r="39" spans="2:28" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -6047,24 +6042,24 @@
     <row r="40" spans="2:28" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B40" s="105"/>
       <c r="C40" s="151"/>
-      <c r="D40" s="248" t="s">
+      <c r="D40" s="214" t="s">
         <v>14</v>
       </c>
-      <c r="E40" s="248"/>
-      <c r="F40" s="248"/>
-      <c r="G40" s="248"/>
-      <c r="H40" s="248"/>
-      <c r="I40" s="248"/>
-      <c r="J40" s="248"/>
-      <c r="K40" s="248"/>
-      <c r="L40" s="248"/>
-      <c r="M40" s="248"/>
-      <c r="N40" s="248"/>
-      <c r="O40" s="248"/>
-      <c r="P40" s="248"/>
-      <c r="Q40" s="248"/>
-      <c r="R40" s="248"/>
-      <c r="S40" s="248"/>
+      <c r="E40" s="214"/>
+      <c r="F40" s="214"/>
+      <c r="G40" s="214"/>
+      <c r="H40" s="214"/>
+      <c r="I40" s="214"/>
+      <c r="J40" s="214"/>
+      <c r="K40" s="214"/>
+      <c r="L40" s="214"/>
+      <c r="M40" s="214"/>
+      <c r="N40" s="214"/>
+      <c r="O40" s="214"/>
+      <c r="P40" s="214"/>
+      <c r="Q40" s="214"/>
+      <c r="R40" s="214"/>
+      <c r="S40" s="214"/>
       <c r="T40" s="152"/>
       <c r="U40" s="106"/>
       <c r="W40" s="132" t="s">
@@ -6074,26 +6069,26 @@
     <row r="41" spans="2:28" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B41" s="105"/>
       <c r="C41" s="151"/>
-      <c r="D41" s="249" t="s">
+      <c r="D41" s="215" t="s">
         <v>4</v>
       </c>
-      <c r="E41" s="249"/>
-      <c r="F41" s="249"/>
-      <c r="G41" s="249"/>
-      <c r="H41" s="249"/>
-      <c r="I41" s="249"/>
-      <c r="J41" s="249"/>
-      <c r="K41" s="249" t="s">
+      <c r="E41" s="215"/>
+      <c r="F41" s="215"/>
+      <c r="G41" s="215"/>
+      <c r="H41" s="215"/>
+      <c r="I41" s="215"/>
+      <c r="J41" s="215"/>
+      <c r="K41" s="215" t="s">
         <v>209</v>
       </c>
-      <c r="L41" s="249"/>
-      <c r="M41" s="249"/>
-      <c r="N41" s="249"/>
-      <c r="O41" s="249"/>
-      <c r="P41" s="249" t="s">
+      <c r="L41" s="215"/>
+      <c r="M41" s="215"/>
+      <c r="N41" s="215"/>
+      <c r="O41" s="215"/>
+      <c r="P41" s="215" t="s">
         <v>78</v>
       </c>
-      <c r="Q41" s="249"/>
+      <c r="Q41" s="215"/>
       <c r="R41" s="146" t="s">
         <v>228</v>
       </c>
@@ -6109,25 +6104,25 @@
       <c r="D42" s="145">
         <v>1</v>
       </c>
-      <c r="E42" s="192" t="str">
+      <c r="E42" s="228" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BE$16,D42+2,FALSE),"")</f>
         <v>L'accès à l'ouvrage et aux équipements de mesure se fait-il en toute sécurité pour les agents en charge des opérations de contrôles et d'entretien ?</v>
       </c>
-      <c r="F42" s="193"/>
-      <c r="G42" s="193"/>
-      <c r="H42" s="193"/>
-      <c r="I42" s="193"/>
-      <c r="J42" s="194"/>
-      <c r="K42" s="192" t="str">
+      <c r="F42" s="229"/>
+      <c r="G42" s="229"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="229"/>
+      <c r="J42" s="230"/>
+      <c r="K42" s="228" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BE$16, D42+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BE$16, D42+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)), "")</f>
         <v>En cas d'accès necessitant des équipements de protection individuels renforcés (ARI par exemple) ou d'intervenir à 2 personnes, retenir "Validé avec réserve"</v>
       </c>
-      <c r="L42" s="193"/>
-      <c r="M42" s="193"/>
-      <c r="N42" s="193"/>
-      <c r="O42" s="194"/>
-      <c r="P42" s="195"/>
-      <c r="Q42" s="196"/>
+      <c r="L42" s="229"/>
+      <c r="M42" s="229"/>
+      <c r="N42" s="229"/>
+      <c r="O42" s="230"/>
+      <c r="P42" s="226"/>
+      <c r="Q42" s="227"/>
       <c r="R42" s="127">
         <f>IF(OR(P42="Validé",P42="Validé avec réserve",P42="Oui"),S42,0)</f>
         <v>0</v>
@@ -6149,25 +6144,25 @@
       <c r="D43" s="145">
         <v>2</v>
       </c>
-      <c r="E43" s="192" t="str">
+      <c r="E43" s="228" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BE$16,D43+2,FALSE),"")</f>
         <v>Le dimensionnement de l'organe de mesure, y compris des canaux d'approche et de fuite, est-il adapté vis-à-vis de l'étendue des débits à mesurer ?</v>
       </c>
-      <c r="F43" s="193"/>
-      <c r="G43" s="193"/>
-      <c r="H43" s="193"/>
-      <c r="I43" s="193"/>
-      <c r="J43" s="194"/>
-      <c r="K43" s="192" t="str">
+      <c r="F43" s="229"/>
+      <c r="G43" s="229"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="229"/>
+      <c r="J43" s="230"/>
+      <c r="K43" s="228" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BE$16, D43+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BE$16, D43+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)), "")</f>
         <v/>
       </c>
-      <c r="L43" s="193"/>
-      <c r="M43" s="193"/>
-      <c r="N43" s="193"/>
-      <c r="O43" s="194"/>
-      <c r="P43" s="195"/>
-      <c r="Q43" s="196"/>
+      <c r="L43" s="229"/>
+      <c r="M43" s="229"/>
+      <c r="N43" s="229"/>
+      <c r="O43" s="230"/>
+      <c r="P43" s="226"/>
+      <c r="Q43" s="227"/>
       <c r="R43" s="127">
         <f t="shared" ref="R43:R51" si="8">IF(OR(P43="Validé",P43="Validé avec réserve",P43="Oui"),S43,0)</f>
         <v>0</v>
@@ -6189,27 +6184,27 @@
       <c r="D44" s="145">
         <v>3</v>
       </c>
-      <c r="E44" s="192" t="str">
+      <c r="E44" s="228" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BE$16,D44+2,FALSE),"")</f>
         <v>L'organe de mesure, y compris les canaux d'approche et de fuite, sont-ils installés conformément aux normes en vigueur et/ou aux prescriptions du constructeur ?
 L'organe de mesure, y compris les canaux d'approche et de fuite, sont-ils déformés ? Dans l'affirmative, est ce que la déformation a un impact significatif sur la mesure de débit ?</v>
       </c>
-      <c r="F44" s="193"/>
-      <c r="G44" s="193"/>
-      <c r="H44" s="193"/>
-      <c r="I44" s="193"/>
-      <c r="J44" s="194"/>
-      <c r="K44" s="192" t="str">
+      <c r="F44" s="229"/>
+      <c r="G44" s="229"/>
+      <c r="H44" s="229"/>
+      <c r="I44" s="229"/>
+      <c r="J44" s="230"/>
+      <c r="K44" s="228" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BE$16, D44+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BE$16, D44+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)), "")</f>
         <v>Le contenu de ce critère sera plus exhaustif (prise de côtes) lorsqu'il s'agit d'un contrôle initial de réception ou lorsqu'il y a une suspicion que le dispositif à "bougé".
 Préciser en commentaire la nature de la déformation et fournir si possible des photos.</v>
       </c>
-      <c r="L44" s="193"/>
-      <c r="M44" s="193"/>
-      <c r="N44" s="193"/>
-      <c r="O44" s="194"/>
-      <c r="P44" s="195"/>
-      <c r="Q44" s="196"/>
+      <c r="L44" s="229"/>
+      <c r="M44" s="229"/>
+      <c r="N44" s="229"/>
+      <c r="O44" s="230"/>
+      <c r="P44" s="226"/>
+      <c r="Q44" s="227"/>
       <c r="R44" s="127">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -6231,26 +6226,26 @@
       <c r="D45" s="145">
         <v>4</v>
       </c>
-      <c r="E45" s="192" t="str">
+      <c r="E45" s="228" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BE$16,D45+2,FALSE),"")</f>
         <v>L'étanchéité, la propreté et l'état d'entretien de l'organe de mesure, des capteurs associés, des canaux d'approche et de fuite sont-ils satisfaisants ?</v>
       </c>
-      <c r="F45" s="193"/>
-      <c r="G45" s="193"/>
-      <c r="H45" s="193"/>
-      <c r="I45" s="193"/>
-      <c r="J45" s="194"/>
-      <c r="K45" s="192" t="str">
+      <c r="F45" s="229"/>
+      <c r="G45" s="229"/>
+      <c r="H45" s="229"/>
+      <c r="I45" s="229"/>
+      <c r="J45" s="230"/>
+      <c r="K45" s="228" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BE$16, D45+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BE$16, D45+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)), "")</f>
         <v>Un défaut de propreté et/ou d'entretien ayant un impact immédiat sur la fiabilité de la mesure doit entrainer un jugement à "Non Validé".
 Un défaut de propreté et/ou d'entretien mais n'ayant à priori pas d'impact immédiat sur la fiabilité de la mesure doit avoir un jugement "Validé avec réserve".</v>
       </c>
-      <c r="L45" s="193"/>
-      <c r="M45" s="193"/>
-      <c r="N45" s="193"/>
-      <c r="O45" s="194"/>
-      <c r="P45" s="195"/>
-      <c r="Q45" s="196"/>
+      <c r="L45" s="229"/>
+      <c r="M45" s="229"/>
+      <c r="N45" s="229"/>
+      <c r="O45" s="230"/>
+      <c r="P45" s="226"/>
+      <c r="Q45" s="227"/>
       <c r="R45" s="127">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -6272,27 +6267,27 @@
       <c r="D46" s="145">
         <v>5</v>
       </c>
-      <c r="E46" s="192" t="str">
+      <c r="E46" s="228" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BE$16,D46+2,FALSE),"")</f>
         <v xml:space="preserve">Le fonctionnement hydraulique de l'organe de mesure, en amont et en aval, est-il satisfaisant ? </v>
       </c>
-      <c r="F46" s="193"/>
-      <c r="G46" s="193"/>
-      <c r="H46" s="193"/>
-      <c r="I46" s="193"/>
-      <c r="J46" s="194"/>
-      <c r="K46" s="192" t="str">
+      <c r="F46" s="229"/>
+      <c r="G46" s="229"/>
+      <c r="H46" s="229"/>
+      <c r="I46" s="229"/>
+      <c r="J46" s="230"/>
+      <c r="K46" s="228" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BE$16, D46+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BE$16, D46+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)), "")</f>
         <v>Une attention particulière devra être apportée  en cas de modification significative des débits, de l'ajout d'un stabilisateur d'écoulement, d'un clapet ou d'un filet à l'exutoire, etc...).
 Les traces de mises en charges peuvent être un indice pour évaluer ce critère.
 En l'absence d'écoulement saisir "Non contrôlé"</v>
       </c>
-      <c r="L46" s="193"/>
-      <c r="M46" s="193"/>
-      <c r="N46" s="193"/>
-      <c r="O46" s="194"/>
-      <c r="P46" s="195"/>
-      <c r="Q46" s="196"/>
+      <c r="L46" s="229"/>
+      <c r="M46" s="229"/>
+      <c r="N46" s="229"/>
+      <c r="O46" s="230"/>
+      <c r="P46" s="226"/>
+      <c r="Q46" s="227"/>
       <c r="R46" s="127">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -6314,26 +6309,26 @@
       <c r="D47" s="145">
         <v>6</v>
       </c>
-      <c r="E47" s="192" t="str">
+      <c r="E47" s="228" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BE$16,D47+2,FALSE),"")</f>
         <v>Le capteur de mesure de hauteur d'eau est-il adapté au type d'effluent et à l'environnement rencontrés (mousses, températures, déchets, etc...) et présente t-il un état de fonctionnement satisfaisant ?
 L'implantation du capteur respecte t-elle les normes en vigueur et/ou les prescriptions du constructeur ?</v>
       </c>
-      <c r="F47" s="193"/>
-      <c r="G47" s="193"/>
-      <c r="H47" s="193"/>
-      <c r="I47" s="193"/>
-      <c r="J47" s="194"/>
-      <c r="K47" s="192" t="str">
+      <c r="F47" s="229"/>
+      <c r="G47" s="229"/>
+      <c r="H47" s="229"/>
+      <c r="I47" s="229"/>
+      <c r="J47" s="230"/>
+      <c r="K47" s="228" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BE$16, D47+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BE$16, D47+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)), "")</f>
         <v/>
       </c>
-      <c r="L47" s="193"/>
-      <c r="M47" s="193"/>
-      <c r="N47" s="193"/>
-      <c r="O47" s="194"/>
-      <c r="P47" s="195"/>
-      <c r="Q47" s="196"/>
+      <c r="L47" s="229"/>
+      <c r="M47" s="229"/>
+      <c r="N47" s="229"/>
+      <c r="O47" s="230"/>
+      <c r="P47" s="226"/>
+      <c r="Q47" s="227"/>
       <c r="R47" s="127">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -6355,28 +6350,28 @@
       <c r="D48" s="145">
         <v>7</v>
       </c>
-      <c r="E48" s="192" t="str">
+      <c r="E48" s="228" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BE$16,D48+2,FALSE),"")</f>
         <v>Les écarts entre d'une part les résultats de mesure des hauteurs d'eau obtenus à partir des dispositifs en place (si possible sur 3 points représentatifs du fonctionnement habituel, plus le 0 hydraulique) et ceux mesurés par l'organisme de contrôle d'autre part, sont-ils cohérents (EMT ± 10 mm) ?</v>
       </c>
-      <c r="F48" s="193"/>
-      <c r="G48" s="193"/>
-      <c r="H48" s="193"/>
-      <c r="I48" s="193"/>
-      <c r="J48" s="194"/>
-      <c r="K48" s="192" t="str">
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="229"/>
+      <c r="I48" s="229"/>
+      <c r="J48" s="230"/>
+      <c r="K48" s="228" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BE$16, D48+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BE$16, D48+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)), "")</f>
         <v/>
       </c>
-      <c r="L48" s="193"/>
-      <c r="M48" s="193"/>
-      <c r="N48" s="193"/>
-      <c r="O48" s="194"/>
-      <c r="P48" s="195" t="str">
+      <c r="L48" s="229"/>
+      <c r="M48" s="229"/>
+      <c r="N48" s="229"/>
+      <c r="O48" s="230"/>
+      <c r="P48" s="226" t="str">
         <f>IF(OR(D40=Critères!J3,D40=Critères!N3,D40=Critères!R3,D40=Critères!V3,D40=Critères!Z3,D40=Critères!AD3),W31,IF(D40=Critères!AL3,W36,"Non contrôlé"))</f>
         <v>Non contrôlé</v>
       </c>
-      <c r="Q48" s="196"/>
+      <c r="Q48" s="227"/>
       <c r="R48" s="127">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -6398,32 +6393,32 @@
       <c r="D49" s="145">
         <v>8</v>
       </c>
-      <c r="E49" s="192" t="str">
+      <c r="E49" s="228" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BE$16,D49+2,FALSE),"")</f>
         <v>La loi hydraulique utilisée Q=f(h), est-elle correctement paramétrée et cohérente avec les caractéristiques de l'organe de mesure ?
 Les écarts entre d'une part les résultats de mesure des débits obtenus à partir des dispositifs en place (si possible sur 3 points représentatifs du fonctionnement habituel ≥ 50 mm) et ceux mesurés par l'organisme de contrôle d'autre part (sur la base de la loi hydraulique fournie par le constructeur), sont-ils cohérents ?
      EMT ± 10% pour une hauteur d'eau comprise entre 50 et 150 mm
      EMT ± 5% pour une hauteur ≥ 150 mm</v>
       </c>
-      <c r="F49" s="193"/>
-      <c r="G49" s="193"/>
-      <c r="H49" s="193"/>
-      <c r="I49" s="193"/>
-      <c r="J49" s="194"/>
-      <c r="K49" s="192" t="str">
+      <c r="F49" s="229"/>
+      <c r="G49" s="229"/>
+      <c r="H49" s="229"/>
+      <c r="I49" s="229"/>
+      <c r="J49" s="230"/>
+      <c r="K49" s="228" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BE$16, D49+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BE$16, D49+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)), "")</f>
         <v>Le contrôle consiste à vérifier le paramétrage exacte de la loi telle que décrite dans la norme, ou pour les autres cas, celle indiquée dans le manuel d'autosurveillance.
 Le nombre de points paramétrés de la courbe de conversion doit également être cohérent avec la gamme des valeurs mesurées.</v>
       </c>
-      <c r="L49" s="193"/>
-      <c r="M49" s="193"/>
-      <c r="N49" s="193"/>
-      <c r="O49" s="194"/>
-      <c r="P49" s="195" t="str">
+      <c r="L49" s="229"/>
+      <c r="M49" s="229"/>
+      <c r="N49" s="229"/>
+      <c r="O49" s="230"/>
+      <c r="P49" s="226" t="str">
         <f>IF(OR(D40=Critères!J3,D40=Critères!N3,D40=Critères!R3,D40=Critères!V3,D40=Critères!Z3,D40=Critères!AD3),X32,"Non contrôlé")</f>
         <v>Non contrôlé</v>
       </c>
-      <c r="Q49" s="196"/>
+      <c r="Q49" s="227"/>
       <c r="R49" s="127">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -6445,31 +6440,31 @@
       <c r="D50" s="145">
         <v>9</v>
       </c>
-      <c r="E50" s="192" t="str">
+      <c r="E50" s="228" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BE$16,D50+2,FALSE),"")</f>
         <v>Les écarts entre d'une part les résultats de mesure des volumes obtenus à partir des dispositifs en place (y compris le report en supervision) et ceux mesurés par l'organisme de contrôle d'autre part, sont-ils cohérents ?  
      EMT ± 10% pour un volume &lt; 50 m3
      EMT ± 5% pour un volume ≥ 50 m3</v>
       </c>
-      <c r="F50" s="193"/>
-      <c r="G50" s="193"/>
-      <c r="H50" s="193"/>
-      <c r="I50" s="193"/>
-      <c r="J50" s="194"/>
-      <c r="K50" s="192" t="str">
+      <c r="F50" s="229"/>
+      <c r="G50" s="229"/>
+      <c r="H50" s="229"/>
+      <c r="I50" s="229"/>
+      <c r="J50" s="230"/>
+      <c r="K50" s="228" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BE$16, D50+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BE$16, D50+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)), "")</f>
         <v>Calcul de l'écart par rapport à la moyenne des 2 valeurs.
 Pour les volumes &lt; 10 m3, le fonctionnement sera apprécié par l'intervenant.</v>
       </c>
-      <c r="L50" s="193"/>
-      <c r="M50" s="193"/>
-      <c r="N50" s="193"/>
-      <c r="O50" s="194"/>
-      <c r="P50" s="195" t="str">
+      <c r="L50" s="229"/>
+      <c r="M50" s="229"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="230"/>
+      <c r="P50" s="226" t="str">
         <f>IF(OR(D40=Critères!J3,D40=Critères!N3,D40=Critères!AD3),W36,"Non contrôlé")</f>
         <v>Non contrôlé</v>
       </c>
-      <c r="Q50" s="196"/>
+      <c r="Q50" s="227"/>
       <c r="R50" s="127">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -6491,25 +6486,25 @@
       <c r="D51" s="145">
         <v>10</v>
       </c>
-      <c r="E51" s="192" t="str">
+      <c r="E51" s="228" t="str">
         <f>IFERROR(HLOOKUP($D$40,Critères!$B$3:$BE$16,D51+2,FALSE),"")</f>
         <v>Existe t-il un dispositif de contrôle adapté et un afficheur de proximité (Hauteur + Débit + Volume) ?</v>
       </c>
-      <c r="F51" s="193"/>
-      <c r="G51" s="193"/>
-      <c r="H51" s="193"/>
-      <c r="I51" s="193"/>
-      <c r="J51" s="194"/>
-      <c r="K51" s="192" t="str">
+      <c r="F51" s="229"/>
+      <c r="G51" s="229"/>
+      <c r="H51" s="229"/>
+      <c r="I51" s="229"/>
+      <c r="J51" s="230"/>
+      <c r="K51" s="228" t="str">
         <f>IFERROR(IF(INDEX(Critères!$B$3:$BE$16, D51+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)="", "", INDEX(Critères!$B$3:$BE$16, D51+2, MATCH($D$40, Critères!$B$3:$BE$3, 0) + 1)), "")</f>
         <v/>
       </c>
-      <c r="L51" s="193"/>
-      <c r="M51" s="193"/>
-      <c r="N51" s="193"/>
-      <c r="O51" s="194"/>
-      <c r="P51" s="195"/>
-      <c r="Q51" s="196"/>
+      <c r="L51" s="229"/>
+      <c r="M51" s="229"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="230"/>
+      <c r="P51" s="226"/>
+      <c r="Q51" s="227"/>
       <c r="R51" s="127">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -6528,54 +6523,54 @@
     <row r="52" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B52" s="105"/>
       <c r="C52" s="151"/>
-      <c r="D52" s="250" t="s">
+      <c r="D52" s="216" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="251"/>
-      <c r="F52" s="251"/>
-      <c r="G52" s="251"/>
-      <c r="H52" s="251"/>
-      <c r="I52" s="251"/>
-      <c r="J52" s="251"/>
-      <c r="K52" s="251"/>
-      <c r="L52" s="251"/>
-      <c r="M52" s="251"/>
-      <c r="N52" s="251"/>
-      <c r="O52" s="252"/>
-      <c r="P52" s="253"/>
-      <c r="Q52" s="253"/>
-      <c r="R52" s="253" t="s">
+      <c r="E52" s="217"/>
+      <c r="F52" s="217"/>
+      <c r="G52" s="217"/>
+      <c r="H52" s="217"/>
+      <c r="I52" s="217"/>
+      <c r="J52" s="217"/>
+      <c r="K52" s="217"/>
+      <c r="L52" s="217"/>
+      <c r="M52" s="217"/>
+      <c r="N52" s="217"/>
+      <c r="O52" s="218"/>
+      <c r="P52" s="219"/>
+      <c r="Q52" s="219"/>
+      <c r="R52" s="219" t="s">
         <v>6</v>
       </c>
-      <c r="S52" s="253"/>
+      <c r="S52" s="219"/>
       <c r="T52" s="152"/>
       <c r="U52" s="106"/>
     </row>
     <row r="53" spans="2:23" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B53" s="105"/>
       <c r="C53" s="151"/>
-      <c r="D53" s="257"/>
-      <c r="E53" s="258"/>
-      <c r="F53" s="258"/>
-      <c r="G53" s="258"/>
-      <c r="H53" s="258"/>
-      <c r="I53" s="258"/>
-      <c r="J53" s="258"/>
-      <c r="K53" s="258"/>
-      <c r="L53" s="258"/>
-      <c r="M53" s="258"/>
-      <c r="N53" s="258"/>
-      <c r="O53" s="259"/>
-      <c r="P53" s="254" t="str">
+      <c r="D53" s="223"/>
+      <c r="E53" s="224"/>
+      <c r="F53" s="224"/>
+      <c r="G53" s="224"/>
+      <c r="H53" s="224"/>
+      <c r="I53" s="224"/>
+      <c r="J53" s="224"/>
+      <c r="K53" s="224"/>
+      <c r="L53" s="224"/>
+      <c r="M53" s="224"/>
+      <c r="N53" s="224"/>
+      <c r="O53" s="225"/>
+      <c r="P53" s="220" t="str">
         <f>IF(R53&gt;80,"Validé",IF(R53&lt;70,"Non Validé", "Validé avec réserve"))</f>
         <v>Non Validé</v>
       </c>
-      <c r="Q53" s="254"/>
-      <c r="R53" s="255">
+      <c r="Q53" s="220"/>
+      <c r="R53" s="221">
         <f>IF(SUM(R42:R51)&gt;100,100,SUM(R42:R51))</f>
         <v>0</v>
       </c>
-      <c r="S53" s="256"/>
+      <c r="S53" s="222"/>
       <c r="T53" s="152"/>
       <c r="U53" s="106"/>
     </row>
@@ -6625,138 +6620,138 @@
     </row>
     <row r="56" spans="2:23" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B56" s="105"/>
-      <c r="C56" s="231" t="s">
+      <c r="C56" s="197" t="s">
         <v>290</v>
       </c>
-      <c r="D56" s="232"/>
-      <c r="E56" s="232"/>
-      <c r="F56" s="232"/>
-      <c r="G56" s="232"/>
-      <c r="H56" s="232"/>
-      <c r="I56" s="232"/>
-      <c r="J56" s="232"/>
-      <c r="K56" s="232"/>
-      <c r="L56" s="232"/>
-      <c r="M56" s="232"/>
-      <c r="N56" s="232"/>
-      <c r="O56" s="232"/>
-      <c r="P56" s="232"/>
-      <c r="Q56" s="232"/>
-      <c r="R56" s="232"/>
-      <c r="S56" s="232"/>
-      <c r="T56" s="233"/>
+      <c r="D56" s="198"/>
+      <c r="E56" s="198"/>
+      <c r="F56" s="198"/>
+      <c r="G56" s="198"/>
+      <c r="H56" s="198"/>
+      <c r="I56" s="198"/>
+      <c r="J56" s="198"/>
+      <c r="K56" s="198"/>
+      <c r="L56" s="198"/>
+      <c r="M56" s="198"/>
+      <c r="N56" s="198"/>
+      <c r="O56" s="198"/>
+      <c r="P56" s="198"/>
+      <c r="Q56" s="198"/>
+      <c r="R56" s="198"/>
+      <c r="S56" s="198"/>
+      <c r="T56" s="199"/>
       <c r="U56" s="106"/>
     </row>
     <row r="57" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B57" s="105"/>
-      <c r="C57" s="241" t="s">
+      <c r="C57" s="207" t="s">
         <v>258</v>
       </c>
-      <c r="D57" s="242"/>
-      <c r="E57" s="242"/>
-      <c r="F57" s="242"/>
-      <c r="G57" s="242"/>
-      <c r="H57" s="242"/>
-      <c r="I57" s="242"/>
-      <c r="J57" s="242"/>
-      <c r="K57" s="242"/>
-      <c r="L57" s="242"/>
-      <c r="M57" s="242"/>
-      <c r="N57" s="242"/>
-      <c r="O57" s="242"/>
-      <c r="P57" s="242"/>
-      <c r="Q57" s="242"/>
-      <c r="R57" s="242"/>
-      <c r="S57" s="242"/>
-      <c r="T57" s="243"/>
+      <c r="D57" s="208"/>
+      <c r="E57" s="208"/>
+      <c r="F57" s="208"/>
+      <c r="G57" s="208"/>
+      <c r="H57" s="208"/>
+      <c r="I57" s="208"/>
+      <c r="J57" s="208"/>
+      <c r="K57" s="208"/>
+      <c r="L57" s="208"/>
+      <c r="M57" s="208"/>
+      <c r="N57" s="208"/>
+      <c r="O57" s="208"/>
+      <c r="P57" s="208"/>
+      <c r="Q57" s="208"/>
+      <c r="R57" s="208"/>
+      <c r="S57" s="208"/>
+      <c r="T57" s="209"/>
       <c r="U57" s="106"/>
     </row>
     <row r="58" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B58" s="105"/>
-      <c r="C58" s="244"/>
-      <c r="D58" s="242"/>
-      <c r="E58" s="242"/>
-      <c r="F58" s="242"/>
-      <c r="G58" s="242"/>
-      <c r="H58" s="242"/>
-      <c r="I58" s="242"/>
-      <c r="J58" s="242"/>
-      <c r="K58" s="242"/>
-      <c r="L58" s="242"/>
-      <c r="M58" s="242"/>
-      <c r="N58" s="242"/>
-      <c r="O58" s="242"/>
-      <c r="P58" s="242"/>
-      <c r="Q58" s="242"/>
-      <c r="R58" s="242"/>
-      <c r="S58" s="242"/>
-      <c r="T58" s="243"/>
+      <c r="C58" s="210"/>
+      <c r="D58" s="208"/>
+      <c r="E58" s="208"/>
+      <c r="F58" s="208"/>
+      <c r="G58" s="208"/>
+      <c r="H58" s="208"/>
+      <c r="I58" s="208"/>
+      <c r="J58" s="208"/>
+      <c r="K58" s="208"/>
+      <c r="L58" s="208"/>
+      <c r="M58" s="208"/>
+      <c r="N58" s="208"/>
+      <c r="O58" s="208"/>
+      <c r="P58" s="208"/>
+      <c r="Q58" s="208"/>
+      <c r="R58" s="208"/>
+      <c r="S58" s="208"/>
+      <c r="T58" s="209"/>
       <c r="U58" s="106"/>
     </row>
     <row r="59" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B59" s="105"/>
-      <c r="C59" s="244"/>
-      <c r="D59" s="242"/>
-      <c r="E59" s="242"/>
-      <c r="F59" s="242"/>
-      <c r="G59" s="242"/>
-      <c r="H59" s="242"/>
-      <c r="I59" s="242"/>
-      <c r="J59" s="242"/>
-      <c r="K59" s="242"/>
-      <c r="L59" s="242"/>
-      <c r="M59" s="242"/>
-      <c r="N59" s="242"/>
-      <c r="O59" s="242"/>
-      <c r="P59" s="242"/>
-      <c r="Q59" s="242"/>
-      <c r="R59" s="242"/>
-      <c r="S59" s="242"/>
-      <c r="T59" s="243"/>
+      <c r="C59" s="210"/>
+      <c r="D59" s="208"/>
+      <c r="E59" s="208"/>
+      <c r="F59" s="208"/>
+      <c r="G59" s="208"/>
+      <c r="H59" s="208"/>
+      <c r="I59" s="208"/>
+      <c r="J59" s="208"/>
+      <c r="K59" s="208"/>
+      <c r="L59" s="208"/>
+      <c r="M59" s="208"/>
+      <c r="N59" s="208"/>
+      <c r="O59" s="208"/>
+      <c r="P59" s="208"/>
+      <c r="Q59" s="208"/>
+      <c r="R59" s="208"/>
+      <c r="S59" s="208"/>
+      <c r="T59" s="209"/>
       <c r="U59" s="106"/>
     </row>
     <row r="60" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B60" s="105"/>
-      <c r="C60" s="244"/>
-      <c r="D60" s="242"/>
-      <c r="E60" s="242"/>
-      <c r="F60" s="242"/>
-      <c r="G60" s="242"/>
-      <c r="H60" s="242"/>
-      <c r="I60" s="242"/>
-      <c r="J60" s="242"/>
-      <c r="K60" s="242"/>
-      <c r="L60" s="242"/>
-      <c r="M60" s="242"/>
-      <c r="N60" s="242"/>
-      <c r="O60" s="242"/>
-      <c r="P60" s="242"/>
-      <c r="Q60" s="242"/>
-      <c r="R60" s="242"/>
-      <c r="S60" s="242"/>
-      <c r="T60" s="243"/>
+      <c r="C60" s="210"/>
+      <c r="D60" s="208"/>
+      <c r="E60" s="208"/>
+      <c r="F60" s="208"/>
+      <c r="G60" s="208"/>
+      <c r="H60" s="208"/>
+      <c r="I60" s="208"/>
+      <c r="J60" s="208"/>
+      <c r="K60" s="208"/>
+      <c r="L60" s="208"/>
+      <c r="M60" s="208"/>
+      <c r="N60" s="208"/>
+      <c r="O60" s="208"/>
+      <c r="P60" s="208"/>
+      <c r="Q60" s="208"/>
+      <c r="R60" s="208"/>
+      <c r="S60" s="208"/>
+      <c r="T60" s="209"/>
       <c r="U60" s="106"/>
     </row>
     <row r="61" spans="2:23" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B61" s="105"/>
-      <c r="C61" s="245"/>
-      <c r="D61" s="246"/>
-      <c r="E61" s="246"/>
-      <c r="F61" s="246"/>
-      <c r="G61" s="246"/>
-      <c r="H61" s="246"/>
-      <c r="I61" s="246"/>
-      <c r="J61" s="246"/>
-      <c r="K61" s="246"/>
-      <c r="L61" s="246"/>
-      <c r="M61" s="246"/>
-      <c r="N61" s="246"/>
-      <c r="O61" s="246"/>
-      <c r="P61" s="246"/>
-      <c r="Q61" s="246"/>
-      <c r="R61" s="246"/>
-      <c r="S61" s="246"/>
-      <c r="T61" s="247"/>
+      <c r="C61" s="211"/>
+      <c r="D61" s="212"/>
+      <c r="E61" s="212"/>
+      <c r="F61" s="212"/>
+      <c r="G61" s="212"/>
+      <c r="H61" s="212"/>
+      <c r="I61" s="212"/>
+      <c r="J61" s="212"/>
+      <c r="K61" s="212"/>
+      <c r="L61" s="212"/>
+      <c r="M61" s="212"/>
+      <c r="N61" s="212"/>
+      <c r="O61" s="212"/>
+      <c r="P61" s="212"/>
+      <c r="Q61" s="212"/>
+      <c r="R61" s="212"/>
+      <c r="S61" s="212"/>
+      <c r="T61" s="213"/>
       <c r="U61" s="106"/>
     </row>
     <row r="62" spans="2:23" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -6783,6 +6778,98 @@
     </row>
   </sheetData>
   <mergeCells count="116">
+    <mergeCell ref="K51:O51"/>
+    <mergeCell ref="P48:Q48"/>
+    <mergeCell ref="E47:J47"/>
+    <mergeCell ref="E48:J48"/>
+    <mergeCell ref="E49:J49"/>
+    <mergeCell ref="E50:J50"/>
+    <mergeCell ref="K43:O43"/>
+    <mergeCell ref="K44:O44"/>
+    <mergeCell ref="K45:O45"/>
+    <mergeCell ref="K46:O46"/>
+    <mergeCell ref="K47:O47"/>
+    <mergeCell ref="K48:O48"/>
+    <mergeCell ref="K49:O49"/>
+    <mergeCell ref="K50:O50"/>
+    <mergeCell ref="P13:S13"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="D24:Q24"/>
+    <mergeCell ref="L11:O11"/>
+    <mergeCell ref="L12:O12"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="P45:Q45"/>
+    <mergeCell ref="P46:Q46"/>
+    <mergeCell ref="P47:Q47"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="L15:O15"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C2:T2"/>
+    <mergeCell ref="N25:Q25"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="L20:O20"/>
+    <mergeCell ref="L21:O21"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="P20:S20"/>
+    <mergeCell ref="P21:S21"/>
+    <mergeCell ref="P22:S22"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G20:K20"/>
+    <mergeCell ref="G21:K21"/>
+    <mergeCell ref="G22:K22"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:S19"/>
+    <mergeCell ref="G18:S18"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="G13:K13"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="K33:M33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:K15"/>
+    <mergeCell ref="L13:O13"/>
+    <mergeCell ref="L14:O14"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="K42:O42"/>
+    <mergeCell ref="E51:J51"/>
+    <mergeCell ref="E42:J42"/>
+    <mergeCell ref="E43:J43"/>
+    <mergeCell ref="E44:J44"/>
+    <mergeCell ref="E45:J45"/>
+    <mergeCell ref="E46:J46"/>
+    <mergeCell ref="R3:T3"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="R5:T5"/>
+    <mergeCell ref="R6:T6"/>
+    <mergeCell ref="C8:T8"/>
+    <mergeCell ref="D10:S10"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="P11:S11"/>
+    <mergeCell ref="P12:S12"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="O3:Q3"/>
     <mergeCell ref="P15:S15"/>
     <mergeCell ref="H25:M25"/>
     <mergeCell ref="P14:S14"/>
@@ -6807,98 +6894,6 @@
     <mergeCell ref="P49:Q49"/>
     <mergeCell ref="P50:Q50"/>
     <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="K42:O42"/>
-    <mergeCell ref="E51:J51"/>
-    <mergeCell ref="E42:J42"/>
-    <mergeCell ref="E43:J43"/>
-    <mergeCell ref="E44:J44"/>
-    <mergeCell ref="E45:J45"/>
-    <mergeCell ref="E46:J46"/>
-    <mergeCell ref="R3:T3"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="R5:T5"/>
-    <mergeCell ref="R6:T6"/>
-    <mergeCell ref="C8:T8"/>
-    <mergeCell ref="D10:S10"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="P11:S11"/>
-    <mergeCell ref="P12:S12"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="G14:K14"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="G13:K13"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="K33:M33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:K15"/>
-    <mergeCell ref="L13:O13"/>
-    <mergeCell ref="L14:O14"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="L15:O15"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C2:T2"/>
-    <mergeCell ref="N25:Q25"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="L20:O20"/>
-    <mergeCell ref="L21:O21"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="P20:S20"/>
-    <mergeCell ref="P21:S21"/>
-    <mergeCell ref="P22:S22"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G20:K20"/>
-    <mergeCell ref="G21:K21"/>
-    <mergeCell ref="G22:K22"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:S19"/>
-    <mergeCell ref="G18:S18"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="P13:S13"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="D24:Q24"/>
-    <mergeCell ref="L11:O11"/>
-    <mergeCell ref="L12:O12"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="P45:Q45"/>
-    <mergeCell ref="P46:Q46"/>
-    <mergeCell ref="P47:Q47"/>
-    <mergeCell ref="P48:Q48"/>
-    <mergeCell ref="E47:J47"/>
-    <mergeCell ref="E48:J48"/>
-    <mergeCell ref="E49:J49"/>
-    <mergeCell ref="E50:J50"/>
-    <mergeCell ref="K43:O43"/>
-    <mergeCell ref="K44:O44"/>
-    <mergeCell ref="K45:O45"/>
-    <mergeCell ref="K46:O46"/>
-    <mergeCell ref="K47:O47"/>
-    <mergeCell ref="K48:O48"/>
-    <mergeCell ref="K49:O49"/>
-    <mergeCell ref="K50:O50"/>
-    <mergeCell ref="K51:O51"/>
   </mergeCells>
   <conditionalFormatting sqref="I27:I30">
     <cfRule type="expression" dxfId="20" priority="16" stopIfTrue="1">
@@ -20788,21 +20783,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B79ED2B215C6A64A8EEA6A4A280DADE5" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3888bf875947002d9437d5c56d07b5d3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="81251141-7599-4081-9962-8622873f55aa" xmlns:ns3="afd5fb63-b61f-423b-93e7-958e038eacd2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="047a8574d06dd2c3496ab08796c0e7b5" ns2:_="" ns3:_="">
     <xsd:import namespace="81251141-7599-4081-9962-8622873f55aa"/>
@@ -21005,32 +20985,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52DDF1-DB9E-4C0C-9E16-F265EDFF44E6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="81251141-7599-4081-9962-8622873f55aa"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="afd5fb63-b61f-423b-93e7-958e038eacd2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB702087-7E88-4AF3-B693-D27B95F8995C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2814875-A1EC-46C5-A2DA-1FD958EE2B85}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21047,4 +21017,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB702087-7E88-4AF3-B693-D27B95F8995C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52DDF1-DB9E-4C0C-9E16-F265EDFF44E6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="81251141-7599-4081-9962-8622873f55aa"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="afd5fb63-b61f-423b-93e7-958e038eacd2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>